--- a/Newdata/今日入庫.xlsx
+++ b/Newdata/今日入庫.xlsx
@@ -11,32 +11,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
+  <si>
+    <t>1600001665</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>PCMCIA CABLE (委託FANUC處理)</t>
+  </si>
+  <si>
+    <t>4T0010</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>陳彥融取</t>
+  </si>
+  <si>
+    <t>5000023180</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>2000007630</t>
+  </si>
   <si>
     <t>1400093971</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>一廠封箱上車</t>
   </si>
   <si>
     <t>2L0003</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>5000022887</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
     <t>100003502</t>
   </si>
   <si>
@@ -74,6 +92,60 @@
   </si>
   <si>
     <t>5000022888</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>8315000470A1</t>
+  </si>
+  <si>
+    <t>Z軸上斜楔_280*239*40(1.5/100)</t>
+  </si>
+  <si>
+    <t>0105</t>
+  </si>
+  <si>
+    <t>3926042199</t>
+  </si>
+  <si>
+    <t>5000023185</t>
+  </si>
+  <si>
+    <t>400006372</t>
+  </si>
+  <si>
+    <t>8810001317A3</t>
+  </si>
+  <si>
+    <t>底座加工圖_5970*2230*558,HSA-327</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>008529</t>
+  </si>
+  <si>
+    <t>5000023183</t>
+  </si>
+  <si>
+    <t>400006466</t>
+  </si>
+  <si>
+    <t>8813001120B3</t>
+  </si>
+  <si>
+    <t>工作台加工圖_HSA-323/327,3000x2200mm</t>
+  </si>
+  <si>
+    <t>008528</t>
+  </si>
+  <si>
+    <t>5000023184</t>
+  </si>
+  <si>
+    <t>400005799</t>
   </si>
   <si>
     <t>採購單</t>
@@ -226,7 +298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="12" customWidth="1"/>
@@ -236,7 +308,7 @@
     <col min="5" max="5" bestFit="1" width="8" customWidth="1"/>
     <col min="6" max="6" bestFit="1" width="6" customWidth="1"/>
     <col min="7" max="7" bestFit="1" width="6" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="8" customWidth="1"/>
+    <col min="8" max="8" bestFit="1" width="12" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="12" customWidth="1"/>
     <col min="10" max="10" bestFit="1" width="13" customWidth="1"/>
     <col min="11" max="11" bestFit="1" width="13" customWidth="1"/>
@@ -247,46 +319,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -312,10 +384,10 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2" s="2">
         <v>46141</v>
@@ -327,15 +399,15 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -344,10 +416,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
@@ -356,7 +428,7 @@
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
@@ -371,7 +443,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3" t="s">
         <v>14</v>
@@ -385,79 +457,255 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G4" t="s">
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K4" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K4" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L4" s="3">
-        <v>2</v>
-      </c>
-      <c r="M4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N4" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="6">
-        <v>4</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N5" s="4" t="s">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K5" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L5" s="3">
+        <v>2</v>
+      </c>
+      <c r="M5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K6" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L6" s="3">
+        <v>40</v>
+      </c>
+      <c r="M6" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K7" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K8" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="6">
+        <v>47</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="4" t="s">
         <v>2</v>
       </c>
     </row>

--- a/Newdata/今日入庫.xlsx
+++ b/Newdata/今日入庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="68">
   <si>
     <t>1600001665</t>
   </si>
@@ -92,6 +92,33 @@
   </si>
   <si>
     <t>5000022888</t>
+  </si>
+  <si>
+    <t>1100097760</t>
+  </si>
+  <si>
+    <t>772700010700</t>
+  </si>
+  <si>
+    <t>H-plus 3-SSD(SATA)_SQF-S25M8-64G-SAC</t>
+  </si>
+  <si>
+    <t>4E0008</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>售服MRP</t>
+  </si>
+  <si>
+    <t>5000023191</t>
+  </si>
+  <si>
+    <t>1100097275</t>
+  </si>
+  <si>
+    <t>5000023192</t>
   </si>
   <si>
     <t>0</t>
@@ -298,13 +325,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="12" customWidth="1"/>
     <col min="2" max="2" bestFit="1" width="4" customWidth="1"/>
     <col min="3" max="3" bestFit="1" width="14" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="37" customWidth="1"/>
+    <col min="4" max="4" bestFit="1" width="38" customWidth="1"/>
     <col min="5" max="5" bestFit="1" width="8" customWidth="1"/>
     <col min="6" max="6" bestFit="1" width="6" customWidth="1"/>
     <col min="7" max="7" bestFit="1" width="6" customWidth="1"/>
@@ -319,46 +346,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -539,10 +566,10 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
@@ -551,19 +578,19 @@
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2">
         <v>46141</v>
@@ -572,42 +599,42 @@
         <v>46141</v>
       </c>
       <c r="L6" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="M6" t="s">
         <v>8</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J7" s="2">
         <v>46141</v>
@@ -622,7 +649,7 @@
         <v>8</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -630,82 +657,170 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
       </c>
       <c r="H8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K8" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L8" s="3">
+        <v>40</v>
+      </c>
+      <c r="M8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" t="s">
         <v>42</v>
       </c>
-      <c r="I8" t="s">
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K8" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="D9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6">
+      <c r="E9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" t="s">
         <v>47</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" s="4" t="s">
+      <c r="J9" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K9" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K10" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="6">
+        <v>49</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="4" t="s">
         <v>2</v>
       </c>
     </row>

--- a/Newdata/今日入庫.xlsx
+++ b/Newdata/今日入庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="74">
   <si>
     <t>1600001665</t>
   </si>
@@ -119,6 +119,24 @@
   </si>
   <si>
     <t>5000023192</t>
+  </si>
+  <si>
+    <t>1100094374</t>
+  </si>
+  <si>
+    <t>8015003001C0</t>
+  </si>
+  <si>
+    <t>接頭座,EM耦合接頭用,AC獨立_L418.5*W428*H86</t>
+  </si>
+  <si>
+    <t>1G0052</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>5000023193</t>
   </si>
   <si>
     <t>0</t>
@@ -325,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="12" customWidth="1"/>
@@ -346,46 +364,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -654,10 +672,10 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -666,16 +684,16 @@
         <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="I8" t="s">
         <v>41</v>
@@ -687,13 +705,13 @@
         <v>46141</v>
       </c>
       <c r="L8" s="3">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="M8" t="s">
         <v>8</v>
       </c>
       <c r="N8" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -701,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
@@ -731,7 +749,7 @@
         <v>46141</v>
       </c>
       <c r="L9" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="M9" t="s">
         <v>8</v>
@@ -745,7 +763,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>49</v>
@@ -757,70 +775,114 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
         <v>5</v>
       </c>
       <c r="H10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K10" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
         <v>51</v>
       </c>
-      <c r="I10" t="s">
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K11" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="6">
         <v>52</v>
       </c>
-      <c r="J10" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K10" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6">
-        <v>49</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" s="4" t="s">
+      <c r="M12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="4" t="s">
         <v>2</v>
       </c>
     </row>

--- a/Newdata/今日入庫.xlsx
+++ b/Newdata/今日入庫.xlsx
@@ -11,35 +11,134 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="219">
+  <si>
+    <t>1400095853</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>8810000887A6 底座滾柱線軌用_MVP-10_研磨</t>
+  </si>
+  <si>
+    <t>1U0016</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>送得金寶-賴宜慧已簽收</t>
+  </si>
+  <si>
+    <t>5000023200</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>400006359</t>
+  </si>
+  <si>
+    <t>1400096925</t>
+  </si>
+  <si>
+    <t>8810001490B1底座HSA216_研磨</t>
+  </si>
+  <si>
+    <t>1T0010</t>
+  </si>
+  <si>
+    <t>5000022026</t>
+  </si>
+  <si>
+    <t>400006523</t>
+  </si>
+  <si>
+    <t>1400096924</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>8810001490B1底座HSA216_銑工</t>
+  </si>
+  <si>
+    <t>3E0001</t>
+  </si>
+  <si>
+    <t>送台典-葉??已簽收</t>
+  </si>
+  <si>
+    <t>5000023199</t>
+  </si>
+  <si>
+    <t>8810001490B1底座HSA216_鑄件</t>
+  </si>
+  <si>
+    <t>5000023198</t>
+  </si>
+  <si>
+    <t>1400097041</t>
+  </si>
+  <si>
+    <t>8811001025C3立柱滾柱線軌用_MVP-8_研磨</t>
+  </si>
+  <si>
+    <t>送得金寶-黃宏達已簽收</t>
+  </si>
+  <si>
+    <t>5000023202</t>
+  </si>
+  <si>
+    <t>400006444</t>
+  </si>
+  <si>
+    <t>1400097040</t>
+  </si>
+  <si>
+    <t>5000023201</t>
+  </si>
+  <si>
+    <t>400006273</t>
+  </si>
+  <si>
+    <t>1400097120</t>
+  </si>
+  <si>
+    <t>893400211300_全罩板金組_HCMC-2110_維修重噴漆</t>
+  </si>
+  <si>
+    <t>2E0004</t>
+  </si>
+  <si>
+    <t>億興廠內噴漆維修，工單:100003502</t>
+  </si>
+  <si>
+    <t>5000023217</t>
+  </si>
+  <si>
+    <t>600003344</t>
+  </si>
   <si>
     <t>1600001665</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>PCMCIA CABLE (委託FANUC處理)</t>
   </si>
   <si>
     <t>4T0010</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>陳彥融取</t>
   </si>
   <si>
     <t>5000023180</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
     <t>2000007630</t>
   </si>
   <si>
@@ -58,6 +157,108 @@
     <t>100003502</t>
   </si>
   <si>
+    <t>1400091836</t>
+  </si>
+  <si>
+    <t>五大鑄件噴漆</t>
+  </si>
+  <si>
+    <t>5000023210</t>
+  </si>
+  <si>
+    <t>100003471</t>
+  </si>
+  <si>
+    <t>1400094421</t>
+  </si>
+  <si>
+    <t>全罩板金噴漆</t>
+  </si>
+  <si>
+    <t>5000023225</t>
+  </si>
+  <si>
+    <t>100003550</t>
+  </si>
+  <si>
+    <t>1400094425</t>
+  </si>
+  <si>
+    <t>5000023224</t>
+  </si>
+  <si>
+    <t>100003552</t>
+  </si>
+  <si>
+    <t>1400091837</t>
+  </si>
+  <si>
+    <t>5000023211</t>
+  </si>
+  <si>
+    <t>1400096626</t>
+  </si>
+  <si>
+    <t>5000023215</t>
+  </si>
+  <si>
+    <t>100003605</t>
+  </si>
+  <si>
+    <t>1300015379</t>
+  </si>
+  <si>
+    <t>出貨補潻費用</t>
+  </si>
+  <si>
+    <t>5000023216</t>
+  </si>
+  <si>
+    <t>1400096963</t>
+  </si>
+  <si>
+    <t>噴漆一小時</t>
+  </si>
+  <si>
+    <t>5000023222</t>
+  </si>
+  <si>
+    <t>100003527</t>
+  </si>
+  <si>
+    <t>1400096965</t>
+  </si>
+  <si>
+    <t>噴漆二小時</t>
+  </si>
+  <si>
+    <t>5000023223</t>
+  </si>
+  <si>
+    <t>100003525</t>
+  </si>
+  <si>
+    <t>1400096750</t>
+  </si>
+  <si>
+    <t>噴漆四小時</t>
+  </si>
+  <si>
+    <t>5000023220</t>
+  </si>
+  <si>
+    <t>100003316</t>
+  </si>
+  <si>
+    <t>1400096950</t>
+  </si>
+  <si>
+    <t>5000023221</t>
+  </si>
+  <si>
+    <t>100003499</t>
+  </si>
+  <si>
     <t>1600001664</t>
   </si>
   <si>
@@ -76,6 +277,159 @@
     <t>2000007631</t>
   </si>
   <si>
+    <t>1400096625</t>
+  </si>
+  <si>
+    <t>機頭噴漆</t>
+  </si>
+  <si>
+    <t>5000023214</t>
+  </si>
+  <si>
+    <t>1400096749</t>
+  </si>
+  <si>
+    <t>5000023213</t>
+  </si>
+  <si>
+    <t>100003615</t>
+  </si>
+  <si>
+    <t>1400096613</t>
+  </si>
+  <si>
+    <t>立式二階梯噴漆</t>
+  </si>
+  <si>
+    <t>5000023212</t>
+  </si>
+  <si>
+    <t>100003515</t>
+  </si>
+  <si>
+    <t>1400088219</t>
+  </si>
+  <si>
+    <t>美國外罩特殊色</t>
+  </si>
+  <si>
+    <t>5000023209</t>
+  </si>
+  <si>
+    <t>100003346</t>
+  </si>
+  <si>
+    <t>1400088213</t>
+  </si>
+  <si>
+    <t>美國水箱特殊色</t>
+  </si>
+  <si>
+    <t>5000023218</t>
+  </si>
+  <si>
+    <t>100003345</t>
+  </si>
+  <si>
+    <t>1400088221</t>
+  </si>
+  <si>
+    <t>5000023205</t>
+  </si>
+  <si>
+    <t>1400088214</t>
+  </si>
+  <si>
+    <t>美國輸送機特殊色</t>
+  </si>
+  <si>
+    <t>5000023219</t>
+  </si>
+  <si>
+    <t>1400088222</t>
+  </si>
+  <si>
+    <t>5000023206</t>
+  </si>
+  <si>
+    <t>1400088224</t>
+  </si>
+  <si>
+    <t>美國鐵屑車特殊色</t>
+  </si>
+  <si>
+    <t>5000023208</t>
+  </si>
+  <si>
+    <t>1400088216</t>
+  </si>
+  <si>
+    <t>5000023204</t>
+  </si>
+  <si>
+    <t>1400088223</t>
+  </si>
+  <si>
+    <t>美國電器箱特殊色</t>
+  </si>
+  <si>
+    <t>5000023207</t>
+  </si>
+  <si>
+    <t>1400088215</t>
+  </si>
+  <si>
+    <t>5000023203</t>
+  </si>
+  <si>
+    <t>1100101511</t>
+  </si>
+  <si>
+    <t>416900013600001</t>
+  </si>
+  <si>
+    <t>溫控面板_E-OK-HB-TMC04-1</t>
+  </si>
+  <si>
+    <t>4H0008</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>售服MRP</t>
+  </si>
+  <si>
+    <t>5000023234</t>
+  </si>
+  <si>
+    <t>416900013700008</t>
+  </si>
+  <si>
+    <t>液溫Sensor_E-OK-SNR-RO-01B</t>
+  </si>
+  <si>
+    <t>5000023235</t>
+  </si>
+  <si>
+    <t>1100101812</t>
+  </si>
+  <si>
+    <t>710700001001</t>
+  </si>
+  <si>
+    <t>PLD-H 08-16-00 HSCI_ID:650891-02</t>
+  </si>
+  <si>
+    <t>4H0001</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>5000023229</t>
+  </si>
+  <si>
     <t>1100095993</t>
   </si>
   <si>
@@ -85,10 +439,7 @@
     <t>三通接頭(H)_368 210-01</t>
   </si>
   <si>
-    <t>4H0001</t>
-  </si>
-  <si>
-    <t>07</t>
+    <t>5000023231</t>
   </si>
   <si>
     <t>5000022888</t>
@@ -106,12 +457,6 @@
     <t>4E0008</t>
   </si>
   <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>售服MRP</t>
-  </si>
-  <si>
     <t>5000023191</t>
   </si>
   <si>
@@ -121,6 +466,42 @@
     <t>5000023192</t>
   </si>
   <si>
+    <t>1100101676</t>
+  </si>
+  <si>
+    <t>792000009700</t>
+  </si>
+  <si>
+    <t>風扇/熱交換器用_6"(HABOR)</t>
+  </si>
+  <si>
+    <t>5000023232</t>
+  </si>
+  <si>
+    <t>0127</t>
+  </si>
+  <si>
+    <t>5000023233</t>
+  </si>
+  <si>
+    <t>1100099048</t>
+  </si>
+  <si>
+    <t>794500082501</t>
+  </si>
+  <si>
+    <t>頭倉接線轉接盒_300*210*90mm</t>
+  </si>
+  <si>
+    <t>1K0005</t>
+  </si>
+  <si>
+    <t>0108</t>
+  </si>
+  <si>
+    <t>5000023227</t>
+  </si>
+  <si>
     <t>1100094374</t>
   </si>
   <si>
@@ -178,6 +559,18 @@
     <t>400006466</t>
   </si>
   <si>
+    <t>8810001490B1</t>
+  </si>
+  <si>
+    <t>底座加工圖_920*2280*4340,HSA216</t>
+  </si>
+  <si>
+    <t>3926042405</t>
+  </si>
+  <si>
+    <t>5000022027</t>
+  </si>
+  <si>
     <t>8813001120B3</t>
   </si>
   <si>
@@ -191,6 +584,48 @@
   </si>
   <si>
     <t>400005799</t>
+  </si>
+  <si>
+    <t>8813001304B0</t>
+  </si>
+  <si>
+    <t>工作台加工圖_2000*1400*200,HSA216</t>
+  </si>
+  <si>
+    <t>3926042243</t>
+  </si>
+  <si>
+    <t>5000022025</t>
+  </si>
+  <si>
+    <t>400006496</t>
+  </si>
+  <si>
+    <t>8822000018B2</t>
+  </si>
+  <si>
+    <t>自動萬向頭本體,A軸加工圖_HF-AU</t>
+  </si>
+  <si>
+    <t>3926042482</t>
+  </si>
+  <si>
+    <t>5000022024</t>
+  </si>
+  <si>
+    <t>400006113</t>
+  </si>
+  <si>
+    <t>893400211300</t>
+  </si>
+  <si>
+    <t>全罩板金組_HCMC-2110</t>
+  </si>
+  <si>
+    <t>0107</t>
+  </si>
+  <si>
+    <t>5000023226</t>
   </si>
   <si>
     <t>採購單</t>
@@ -343,17 +778,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="12" customWidth="1"/>
     <col min="2" max="2" bestFit="1" width="4" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="14" customWidth="1"/>
+    <col min="3" max="3" bestFit="1" width="17" customWidth="1"/>
     <col min="4" max="4" bestFit="1" width="38" customWidth="1"/>
     <col min="5" max="5" bestFit="1" width="8" customWidth="1"/>
     <col min="6" max="6" bestFit="1" width="6" customWidth="1"/>
     <col min="7" max="7" bestFit="1" width="6" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="12" customWidth="1"/>
+    <col min="8" max="8" bestFit="1" width="23" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="12" customWidth="1"/>
     <col min="10" max="10" bestFit="1" width="13" customWidth="1"/>
     <col min="11" max="11" bestFit="1" width="13" customWidth="1"/>
@@ -364,46 +799,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>208</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>67</v>
+        <v>212</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -441,7 +876,7 @@
         <v>46141</v>
       </c>
       <c r="L2" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="s">
         <v>8</v>
@@ -499,16 +934,16 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
@@ -517,10 +952,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2">
         <v>46141</v>
@@ -535,37 +970,37 @@
         <v>8</v>
       </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
       <c r="J5" s="2">
         <v>46141</v>
       </c>
@@ -573,218 +1008,218 @@
         <v>46141</v>
       </c>
       <c r="L5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" t="s">
         <v>8</v>
       </c>
       <c r="N5" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K6" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K6" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
+      <c r="J7" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K7" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L7" s="3">
+        <v>2</v>
+      </c>
+      <c r="M7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" t="s">
         <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K7" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K8" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" t="s">
         <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K8" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3</v>
-      </c>
-      <c r="M8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K9" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K9" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L9" s="3">
-        <v>40</v>
-      </c>
-      <c r="M9" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G10" t="s">
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="I10" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2">
         <v>46141</v>
@@ -799,90 +1234,1850 @@
         <v>8</v>
       </c>
       <c r="N10" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K11" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K12" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" t="s">
         <v>55</v>
       </c>
-      <c r="D11" t="s">
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
         <v>56</v>
       </c>
-      <c r="E11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K13" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L13" s="3">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K14" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" t="s">
         <v>51</v>
       </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K11" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L11" s="3">
-        <v>1</v>
-      </c>
-      <c r="M11" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="6">
-        <v>52</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="4" t="s">
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K15" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K16" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L16" s="3">
+        <v>19</v>
+      </c>
+      <c r="M16" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K17" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K18" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K19" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K20" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K21" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>90</v>
+      </c>
+      <c r="J22" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K22" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>92</v>
+      </c>
+      <c r="J23" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K23" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" t="s">
+        <v>96</v>
+      </c>
+      <c r="J24" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K24" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1</v>
+      </c>
+      <c r="M24" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" t="s">
+        <v>100</v>
+      </c>
+      <c r="J25" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K25" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L25" s="3">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>104</v>
+      </c>
+      <c r="J26" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K26" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K27" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" t="s">
+        <v>110</v>
+      </c>
+      <c r="J28" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K28" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L28" s="3">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>8</v>
+      </c>
+      <c r="N28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" t="s">
+        <v>112</v>
+      </c>
+      <c r="J29" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K29" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L29" s="3">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" t="s">
+        <v>115</v>
+      </c>
+      <c r="J30" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K30" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L30" s="3">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>8</v>
+      </c>
+      <c r="N30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>117</v>
+      </c>
+      <c r="J31" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K31" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L31" s="3">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>8</v>
+      </c>
+      <c r="N31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" t="s">
+        <v>120</v>
+      </c>
+      <c r="J32" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K32" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L32" s="3">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" t="s">
+        <v>122</v>
+      </c>
+      <c r="J33" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K33" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L33" s="3">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" t="s">
+        <v>127</v>
+      </c>
+      <c r="G34" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I34" t="s">
+        <v>129</v>
+      </c>
+      <c r="J34" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K34" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L34" s="3">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>8</v>
+      </c>
+      <c r="N34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" t="s">
+        <v>126</v>
+      </c>
+      <c r="F35" t="s">
+        <v>127</v>
+      </c>
+      <c r="G35" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" t="s">
+        <v>132</v>
+      </c>
+      <c r="J35" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K35" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L35" s="3">
+        <v>5</v>
+      </c>
+      <c r="M35" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" t="s">
+        <v>137</v>
+      </c>
+      <c r="G36" t="s">
+        <v>5</v>
+      </c>
+      <c r="H36" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>138</v>
+      </c>
+      <c r="J36" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K36" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L36" s="3">
+        <v>2</v>
+      </c>
+      <c r="M36" t="s">
+        <v>8</v>
+      </c>
+      <c r="N36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" t="s">
+        <v>137</v>
+      </c>
+      <c r="G37" t="s">
+        <v>5</v>
+      </c>
+      <c r="H37" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" t="s">
+        <v>142</v>
+      </c>
+      <c r="J37" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K37" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L37" s="3">
+        <v>2</v>
+      </c>
+      <c r="M37" t="s">
+        <v>8</v>
+      </c>
+      <c r="N37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" t="s">
+        <v>136</v>
+      </c>
+      <c r="F38" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" t="s">
+        <v>5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>2</v>
+      </c>
+      <c r="I38" t="s">
+        <v>143</v>
+      </c>
+      <c r="J38" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K38" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L38" s="3">
+        <v>2</v>
+      </c>
+      <c r="M38" t="s">
+        <v>8</v>
+      </c>
+      <c r="N38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>128</v>
+      </c>
+      <c r="I39" t="s">
+        <v>148</v>
+      </c>
+      <c r="J39" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K39" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L39" s="3">
+        <v>1</v>
+      </c>
+      <c r="M39" t="s">
+        <v>8</v>
+      </c>
+      <c r="N39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" t="s">
+        <v>127</v>
+      </c>
+      <c r="G40" t="s">
+        <v>5</v>
+      </c>
+      <c r="H40" t="s">
+        <v>128</v>
+      </c>
+      <c r="I40" t="s">
+        <v>150</v>
+      </c>
+      <c r="J40" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K40" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L40" s="3">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
+        <v>8</v>
+      </c>
+      <c r="N40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" t="s">
+        <v>153</v>
+      </c>
+      <c r="E41" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" t="s">
+        <v>127</v>
+      </c>
+      <c r="G41" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" t="s">
+        <v>128</v>
+      </c>
+      <c r="I41" t="s">
+        <v>154</v>
+      </c>
+      <c r="J41" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K41" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L41" s="3">
+        <v>1</v>
+      </c>
+      <c r="M41" t="s">
+        <v>8</v>
+      </c>
+      <c r="N41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" t="s">
+        <v>153</v>
+      </c>
+      <c r="E42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" t="s">
+        <v>5</v>
+      </c>
+      <c r="H42" t="s">
+        <v>128</v>
+      </c>
+      <c r="I42" t="s">
+        <v>156</v>
+      </c>
+      <c r="J42" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K42" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L42" s="3">
+        <v>8</v>
+      </c>
+      <c r="M42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" t="s">
+        <v>161</v>
+      </c>
+      <c r="G43" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" t="s">
+        <v>162</v>
+      </c>
+      <c r="J43" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K43" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L43" s="3">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" t="s">
+        <v>165</v>
+      </c>
+      <c r="E44" t="s">
+        <v>166</v>
+      </c>
+      <c r="F44" t="s">
+        <v>167</v>
+      </c>
+      <c r="G44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" t="s">
+        <v>168</v>
+      </c>
+      <c r="J44" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K44" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L44" s="3">
+        <v>3</v>
+      </c>
+      <c r="M44" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>172</v>
+      </c>
+      <c r="G45" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" t="s">
+        <v>173</v>
+      </c>
+      <c r="I45" t="s">
+        <v>174</v>
+      </c>
+      <c r="J45" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K45" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L45" s="3">
+        <v>40</v>
+      </c>
+      <c r="M45" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>169</v>
+      </c>
+      <c r="C46" t="s">
+        <v>176</v>
+      </c>
+      <c r="D46" t="s">
+        <v>177</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46" t="s">
+        <v>178</v>
+      </c>
+      <c r="G46" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" t="s">
+        <v>179</v>
+      </c>
+      <c r="I46" t="s">
+        <v>180</v>
+      </c>
+      <c r="J46" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K46" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L46" s="3">
+        <v>1</v>
+      </c>
+      <c r="M46" t="s">
+        <v>8</v>
+      </c>
+      <c r="N46" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" t="s">
+        <v>183</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>178</v>
+      </c>
+      <c r="G47" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" t="s">
+        <v>184</v>
+      </c>
+      <c r="I47" t="s">
+        <v>185</v>
+      </c>
+      <c r="J47" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K47" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L47" s="3">
+        <v>1</v>
+      </c>
+      <c r="M47" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" t="s">
+        <v>187</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48" t="s">
+        <v>178</v>
+      </c>
+      <c r="G48" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" t="s">
+        <v>188</v>
+      </c>
+      <c r="I48" t="s">
+        <v>189</v>
+      </c>
+      <c r="J48" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K48" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L48" s="3">
+        <v>1</v>
+      </c>
+      <c r="M48" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>2</v>
+      </c>
+      <c r="B49" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" t="s">
+        <v>191</v>
+      </c>
+      <c r="D49" t="s">
+        <v>192</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49" t="s">
+        <v>178</v>
+      </c>
+      <c r="G49" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" t="s">
+        <v>193</v>
+      </c>
+      <c r="I49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J49" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K49" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L49" s="3">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>8</v>
+      </c>
+      <c r="N49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50" t="s">
+        <v>197</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" t="s">
+        <v>167</v>
+      </c>
+      <c r="G50" t="s">
+        <v>5</v>
+      </c>
+      <c r="H50" t="s">
+        <v>198</v>
+      </c>
+      <c r="I50" t="s">
+        <v>199</v>
+      </c>
+      <c r="J50" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K50" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L50" s="3">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>8</v>
+      </c>
+      <c r="N50" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" t="s">
+        <v>201</v>
+      </c>
+      <c r="D51" t="s">
+        <v>202</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>203</v>
+      </c>
+      <c r="G51" t="s">
+        <v>5</v>
+      </c>
+      <c r="H51" t="s">
+        <v>34</v>
+      </c>
+      <c r="I51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J51" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K51" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L51" s="3">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
+        <v>8</v>
+      </c>
+      <c r="N51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="6">
+        <v>126</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="4" t="s">
         <v>2</v>
       </c>
     </row>

--- a/Newdata/今日入庫.xlsx
+++ b/Newdata/今日入庫.xlsx
@@ -11,38 +11,62 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="461">
+  <si>
+    <t>1400096974</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>8810000887A6 底座滾柱線軌用_MVP-10_研磨</t>
+  </si>
+  <si>
+    <t>1U0016</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>元榮維修歸還，工單:100003573</t>
+  </si>
+  <si>
+    <t>5000023250</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>600003364</t>
+  </si>
   <si>
     <t>1400095853</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>8810000887A6 底座滾柱線軌用_MVP-10_研磨</t>
-  </si>
-  <si>
-    <t>1U0016</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>送得金寶-賴宜慧已簽收</t>
   </si>
   <si>
     <t>5000023200</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
     <t>400006359</t>
   </si>
   <si>
+    <t>1400096407</t>
+  </si>
+  <si>
+    <t>8810001281C2底座_HCMC-1682_研磨</t>
+  </si>
+  <si>
+    <t>5000023251</t>
+  </si>
+  <si>
+    <t>400006385</t>
+  </si>
+  <si>
     <t>1400096925</t>
   </si>
   <si>
@@ -106,6 +130,75 @@
     <t>400006273</t>
   </si>
   <si>
+    <t>1400096972</t>
+  </si>
+  <si>
+    <t>8811001291B0立柱_SMC-5_研磨</t>
+  </si>
+  <si>
+    <t>元榮維修歸還，工單:100003499</t>
+  </si>
+  <si>
+    <t>5000023249</t>
+  </si>
+  <si>
+    <t>600003362</t>
+  </si>
+  <si>
+    <t>1400097052</t>
+  </si>
+  <si>
+    <t>8813001043A2工作台_S-Plus8_研磨</t>
+  </si>
+  <si>
+    <t>1G0047</t>
+  </si>
+  <si>
+    <t>廣嘉宏維修歸還，工單:100003594</t>
+  </si>
+  <si>
+    <t>5000023254</t>
+  </si>
+  <si>
+    <t>600003365</t>
+  </si>
+  <si>
+    <t>1400091367</t>
+  </si>
+  <si>
+    <t>8817000516A6_ 橫樑滑座加工圖1927Lx1100Wx727.5H,</t>
+  </si>
+  <si>
+    <t>1G0014</t>
+  </si>
+  <si>
+    <t>ZY-911，送三廠，陳錫賢已簽收</t>
+  </si>
+  <si>
+    <t>5000023253</t>
+  </si>
+  <si>
+    <t>400006043</t>
+  </si>
+  <si>
+    <t>1400095766</t>
+  </si>
+  <si>
+    <t>891000067602-CTS過濾水車組,40bar_簡易型PFA60</t>
+  </si>
+  <si>
+    <t>4U0011</t>
+  </si>
+  <si>
+    <t>10000356，送三廠，李堂已簽收</t>
+  </si>
+  <si>
+    <t>5000023237</t>
+  </si>
+  <si>
+    <t>500006815</t>
+  </si>
+  <si>
     <t>1400097120</t>
   </si>
   <si>
@@ -124,6 +217,21 @@
     <t>600003344</t>
   </si>
   <si>
+    <t>1400093206</t>
+  </si>
+  <si>
+    <t>CTS板金噴漆</t>
+  </si>
+  <si>
+    <t>2M0006</t>
+  </si>
+  <si>
+    <t>5000023240</t>
+  </si>
+  <si>
+    <t>100003510</t>
+  </si>
+  <si>
     <t>1600001665</t>
   </si>
   <si>
@@ -142,6 +250,21 @@
     <t>2000007630</t>
   </si>
   <si>
+    <t>1300015263</t>
+  </si>
+  <si>
+    <t>SGS儀器校正_花岡石四方規</t>
+  </si>
+  <si>
+    <t>5T0020</t>
+  </si>
+  <si>
+    <t>品管課-顏宇萱已簽收</t>
+  </si>
+  <si>
+    <t>5000023245</t>
+  </si>
+  <si>
     <t>1400093971</t>
   </si>
   <si>
@@ -157,6 +280,21 @@
     <t>100003502</t>
   </si>
   <si>
+    <t>1400092562</t>
+  </si>
+  <si>
+    <t>三廠上車2箱</t>
+  </si>
+  <si>
+    <t>5L0116</t>
+  </si>
+  <si>
+    <t>5000023252</t>
+  </si>
+  <si>
+    <t>100003410</t>
+  </si>
+  <si>
     <t>1400091836</t>
   </si>
   <si>
@@ -169,6 +307,21 @@
     <t>100003471</t>
   </si>
   <si>
+    <t>1700000204</t>
+  </si>
+  <si>
+    <t>五軸機型專用電子水平儀</t>
+  </si>
+  <si>
+    <t>4Z0028</t>
+  </si>
+  <si>
+    <t>品管課-郭家宏已簽收</t>
+  </si>
+  <si>
+    <t>5000023244</t>
+  </si>
+  <si>
     <t>1400094421</t>
   </si>
   <si>
@@ -190,21 +343,21 @@
     <t>100003552</t>
   </si>
   <si>
+    <t>1400096626</t>
+  </si>
+  <si>
+    <t>5000023215</t>
+  </si>
+  <si>
+    <t>100003605</t>
+  </si>
+  <si>
     <t>1400091837</t>
   </si>
   <si>
     <t>5000023211</t>
   </si>
   <si>
-    <t>1400096626</t>
-  </si>
-  <si>
-    <t>5000023215</t>
-  </si>
-  <si>
-    <t>100003605</t>
-  </si>
-  <si>
     <t>1300015379</t>
   </si>
   <si>
@@ -214,6 +367,48 @@
     <t>5000023216</t>
   </si>
   <si>
+    <t>1300015301</t>
+  </si>
+  <si>
+    <t>切削液BOTON S-550Y-18L</t>
+  </si>
+  <si>
+    <t>4T0056</t>
+  </si>
+  <si>
+    <t>應用技術與測試驗證部-趙子桂已簽收</t>
+  </si>
+  <si>
+    <t>5000023238</t>
+  </si>
+  <si>
+    <t>1300015138</t>
+  </si>
+  <si>
+    <t>前瞻技術中心增設2支網路攝影機</t>
+  </si>
+  <si>
+    <t>5C0266</t>
+  </si>
+  <si>
+    <t>資訊管理部-詹啟東已簽收</t>
+  </si>
+  <si>
+    <t>5000023248</t>
+  </si>
+  <si>
+    <t>1300015298</t>
+  </si>
+  <si>
+    <t>品質管制部儀器測量專用筆記型電腦(HP ProBook 460 G11)</t>
+  </si>
+  <si>
+    <t>5C0133</t>
+  </si>
+  <si>
+    <t>5000023247</t>
+  </si>
+  <si>
     <t>1400096963</t>
   </si>
   <si>
@@ -238,27 +433,27 @@
     <t>100003525</t>
   </si>
   <si>
+    <t>1400096950</t>
+  </si>
+  <si>
+    <t>噴漆四小時</t>
+  </si>
+  <si>
+    <t>5000023221</t>
+  </si>
+  <si>
+    <t>100003499</t>
+  </si>
+  <si>
     <t>1400096750</t>
   </si>
   <si>
-    <t>噴漆四小時</t>
-  </si>
-  <si>
     <t>5000023220</t>
   </si>
   <si>
     <t>100003316</t>
   </si>
   <si>
-    <t>1400096950</t>
-  </si>
-  <si>
-    <t>5000023221</t>
-  </si>
-  <si>
-    <t>100003499</t>
-  </si>
-  <si>
     <t>1600001664</t>
   </si>
   <si>
@@ -277,6 +472,18 @@
     <t>2000007631</t>
   </si>
   <si>
+    <t>1300015306</t>
+  </si>
+  <si>
+    <t>栓牙規_M36 x 4.0-6H</t>
+  </si>
+  <si>
+    <t>4Z0002</t>
+  </si>
+  <si>
+    <t>5000023243</t>
+  </si>
+  <si>
     <t>1400096625</t>
   </si>
   <si>
@@ -307,6 +514,33 @@
     <t>100003515</t>
   </si>
   <si>
+    <t>1600001661</t>
+  </si>
+  <si>
+    <t>第四軸中版平面度研磨 (委託盛鈺處理) NO:SQ1150325003</t>
+  </si>
+  <si>
+    <t>4S0035</t>
+  </si>
+  <si>
+    <t>售服-陳昭利已簽收</t>
+  </si>
+  <si>
+    <t>5000023239</t>
+  </si>
+  <si>
+    <t>2000007505</t>
+  </si>
+  <si>
+    <t>1300015299</t>
+  </si>
+  <si>
+    <t>羅技 M90 USB有線滑鼠</t>
+  </si>
+  <si>
+    <t>5000023246</t>
+  </si>
+  <si>
     <t>1400088219</t>
   </si>
   <si>
@@ -319,24 +553,33 @@
     <t>100003346</t>
   </si>
   <si>
+    <t>1400095832</t>
+  </si>
+  <si>
+    <t>5000023241</t>
+  </si>
+  <si>
+    <t>100003186</t>
+  </si>
+  <si>
+    <t>1400088221</t>
+  </si>
+  <si>
+    <t>美國水箱特殊色</t>
+  </si>
+  <si>
+    <t>5000023205</t>
+  </si>
+  <si>
     <t>1400088213</t>
   </si>
   <si>
-    <t>美國水箱特殊色</t>
-  </si>
-  <si>
     <t>5000023218</t>
   </si>
   <si>
     <t>100003345</t>
   </si>
   <si>
-    <t>1400088221</t>
-  </si>
-  <si>
-    <t>5000023205</t>
-  </si>
-  <si>
     <t>1400088214</t>
   </si>
   <si>
@@ -352,21 +595,21 @@
     <t>5000023206</t>
   </si>
   <si>
+    <t>1400088216</t>
+  </si>
+  <si>
+    <t>美國鐵屑車特殊色</t>
+  </si>
+  <si>
+    <t>5000023204</t>
+  </si>
+  <si>
     <t>1400088224</t>
   </si>
   <si>
-    <t>美國鐵屑車特殊色</t>
-  </si>
-  <si>
     <t>5000023208</t>
   </si>
   <si>
-    <t>1400088216</t>
-  </si>
-  <si>
-    <t>5000023204</t>
-  </si>
-  <si>
     <t>1400088223</t>
   </si>
   <si>
@@ -382,6 +625,15 @@
     <t>5000023203</t>
   </si>
   <si>
+    <t>1300015341</t>
+  </si>
+  <si>
+    <t>量具維修-20901070-槓桿式針盤指示錶</t>
+  </si>
+  <si>
+    <t>5000023242</t>
+  </si>
+  <si>
     <t>1100101511</t>
   </si>
   <si>
@@ -403,6 +655,18 @@
     <t>5000023234</t>
   </si>
   <si>
+    <t>1100101596</t>
+  </si>
+  <si>
+    <t>416900013600006</t>
+  </si>
+  <si>
+    <t>油壓開關_S-PS-S973</t>
+  </si>
+  <si>
+    <t>5000023236</t>
+  </si>
+  <si>
     <t>416900013700008</t>
   </si>
   <si>
@@ -466,6 +730,450 @@
     <t>5000023192</t>
   </si>
   <si>
+    <t>1100101742</t>
+  </si>
+  <si>
+    <t>786600002800</t>
+  </si>
+  <si>
+    <t>MP156底板電料_FANUC+單螢幕,三菱廠牌電磁接觸</t>
+  </si>
+  <si>
+    <t>4C0142</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>5000023313</t>
+  </si>
+  <si>
+    <t>1100101739</t>
+  </si>
+  <si>
+    <t>786600003800</t>
+  </si>
+  <si>
+    <t>MP158底板電料_三菱</t>
+  </si>
+  <si>
+    <t>5000023304</t>
+  </si>
+  <si>
+    <t>1100101755</t>
+  </si>
+  <si>
+    <t>786600004900</t>
+  </si>
+  <si>
+    <t>MP191底板電料_FANUC+單螢幕,TE廠牌電磁接觸器</t>
+  </si>
+  <si>
+    <t>4G0119</t>
+  </si>
+  <si>
+    <t>100003612</t>
+  </si>
+  <si>
+    <t>5000023283</t>
+  </si>
+  <si>
+    <t>1100101752</t>
+  </si>
+  <si>
+    <t>786600005100</t>
+  </si>
+  <si>
+    <t>MP191底板電料_三菱,TE廠牌電磁接觸器</t>
+  </si>
+  <si>
+    <t>100003604</t>
+  </si>
+  <si>
+    <t>5000023277</t>
+  </si>
+  <si>
+    <t>1100101756</t>
+  </si>
+  <si>
+    <t>786600005300</t>
+  </si>
+  <si>
+    <t>MP191底板電料_FANUC+單螢幕,三菱廠牌電磁接觸</t>
+  </si>
+  <si>
+    <t>100003614</t>
+  </si>
+  <si>
+    <t>5000023289</t>
+  </si>
+  <si>
+    <t>1100099792</t>
+  </si>
+  <si>
+    <t>786600006400</t>
+  </si>
+  <si>
+    <t>MP202底板電料_FANUC+雙螢幕</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>5000023255</t>
+  </si>
+  <si>
+    <t>1100100793</t>
+  </si>
+  <si>
+    <t>786600006800</t>
+  </si>
+  <si>
+    <t>MP205底板電料_FANUC+單螢幕</t>
+  </si>
+  <si>
+    <t>100003580</t>
+  </si>
+  <si>
+    <t>5000023262</t>
+  </si>
+  <si>
+    <t>1100101749</t>
+  </si>
+  <si>
+    <t>786600007000</t>
+  </si>
+  <si>
+    <t>MP205底板電料_三菱</t>
+  </si>
+  <si>
+    <t>100003596</t>
+  </si>
+  <si>
+    <t>5000023267</t>
+  </si>
+  <si>
+    <t>1100101738</t>
+  </si>
+  <si>
+    <t>786600007100</t>
+  </si>
+  <si>
+    <t>MP205底板電料_協鴻</t>
+  </si>
+  <si>
+    <t>100003602</t>
+  </si>
+  <si>
+    <t>5000023296</t>
+  </si>
+  <si>
+    <t>1100101741</t>
+  </si>
+  <si>
+    <t>786600007400</t>
+  </si>
+  <si>
+    <t>MP191底板電料_協鴻,TE廠牌電磁接觸器</t>
+  </si>
+  <si>
+    <t>100003611</t>
+  </si>
+  <si>
+    <t>5000023308</t>
+  </si>
+  <si>
+    <t>1100101751</t>
+  </si>
+  <si>
+    <t>786600019400</t>
+  </si>
+  <si>
+    <t>MP229底板電料_協鴻</t>
+  </si>
+  <si>
+    <t>100003601</t>
+  </si>
+  <si>
+    <t>5000023270</t>
+  </si>
+  <si>
+    <t>786700000200</t>
+  </si>
+  <si>
+    <t>ATC刀庫電料_TE,雙馬達</t>
+  </si>
+  <si>
+    <t>5000023297</t>
+  </si>
+  <si>
+    <t>5000023284</t>
+  </si>
+  <si>
+    <t>5000023309</t>
+  </si>
+  <si>
+    <t>5000023278</t>
+  </si>
+  <si>
+    <t>5000023271</t>
+  </si>
+  <si>
+    <t>5000023263</t>
+  </si>
+  <si>
+    <t>5000023305</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>786700000500</t>
+  </si>
+  <si>
+    <t>CE底板電料_無刀庫門</t>
+  </si>
+  <si>
+    <t>5000023272</t>
+  </si>
+  <si>
+    <t>786700000700</t>
+  </si>
+  <si>
+    <t>捲屑馬達電料_TE</t>
+  </si>
+  <si>
+    <t>5000023310</t>
+  </si>
+  <si>
+    <t>5000023298</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>5000023273</t>
+  </si>
+  <si>
+    <t>5000023306</t>
+  </si>
+  <si>
+    <t>5000023264</t>
+  </si>
+  <si>
+    <t>5000023259</t>
+  </si>
+  <si>
+    <t>786700000800</t>
+  </si>
+  <si>
+    <t>沖屑裝置電料_TE</t>
+  </si>
+  <si>
+    <t>5000023265</t>
+  </si>
+  <si>
+    <t>5000023268</t>
+  </si>
+  <si>
+    <t>5000023311</t>
+  </si>
+  <si>
+    <t>5000023274</t>
+  </si>
+  <si>
+    <t>5000023258</t>
+  </si>
+  <si>
+    <t>5000023279</t>
+  </si>
+  <si>
+    <t>5000023299</t>
+  </si>
+  <si>
+    <t>5000023285</t>
+  </si>
+  <si>
+    <t>786700001200</t>
+  </si>
+  <si>
+    <t>立式油壓箱電料_TE</t>
+  </si>
+  <si>
+    <t>5000023257</t>
+  </si>
+  <si>
+    <t>5000023300</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>786700001300</t>
+  </si>
+  <si>
+    <t>排屑機電料_TE</t>
+  </si>
+  <si>
+    <t>5000023260</t>
+  </si>
+  <si>
+    <t>5000023280</t>
+  </si>
+  <si>
+    <t>5000023286</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>786700001400</t>
+  </si>
+  <si>
+    <t>簡易式CTS無水車電料_TE</t>
+  </si>
+  <si>
+    <t>5000023261</t>
+  </si>
+  <si>
+    <t>5000023275</t>
+  </si>
+  <si>
+    <t>5000023301</t>
+  </si>
+  <si>
+    <t>786700001600</t>
+  </si>
+  <si>
+    <t>ATC刀庫電料_三菱,雙馬達</t>
+  </si>
+  <si>
+    <t>5000023314</t>
+  </si>
+  <si>
+    <t>5000023290</t>
+  </si>
+  <si>
+    <t>786700001700</t>
+  </si>
+  <si>
+    <t>捲屑馬達電料_三菱</t>
+  </si>
+  <si>
+    <t>5000023291</t>
+  </si>
+  <si>
+    <t>786700001800</t>
+  </si>
+  <si>
+    <t>沖屑裝置電料_三菱</t>
+  </si>
+  <si>
+    <t>5000023315</t>
+  </si>
+  <si>
+    <t>5000023292</t>
+  </si>
+  <si>
+    <t>786700001900</t>
+  </si>
+  <si>
+    <t>立式油壓箱電料_三菱</t>
+  </si>
+  <si>
+    <t>5000023293</t>
+  </si>
+  <si>
+    <t>786700002700</t>
+  </si>
+  <si>
+    <t>ATC變極刀庫電料_TE,雙馬達</t>
+  </si>
+  <si>
+    <t>5000023256</t>
+  </si>
+  <si>
+    <t>786700003100</t>
+  </si>
+  <si>
+    <t>TS電料_三菱,發那科,協鴻</t>
+  </si>
+  <si>
+    <t>5000023287</t>
+  </si>
+  <si>
+    <t>5000023294</t>
+  </si>
+  <si>
+    <t>5000023281</t>
+  </si>
+  <si>
+    <t>5000023302</t>
+  </si>
+  <si>
+    <t>786700004400</t>
+  </si>
+  <si>
+    <t>立式Q1動力電料14mm非AC220_GB,NR12,一般立式小</t>
+  </si>
+  <si>
+    <t>5000023316</t>
+  </si>
+  <si>
+    <t>5000023312</t>
+  </si>
+  <si>
+    <t>5000023269</t>
+  </si>
+  <si>
+    <t>786700004500</t>
+  </si>
+  <si>
+    <t>立式Q1動力電料22mmAC220_TS立式小</t>
+  </si>
+  <si>
+    <t>5000023288</t>
+  </si>
+  <si>
+    <t>5000023295</t>
+  </si>
+  <si>
+    <t>5000023282</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>5000023303</t>
+  </si>
+  <si>
+    <t>786700004800</t>
+  </si>
+  <si>
+    <t>立式Q1動力電料22mm非AC220_GB,NR12,一般立式小</t>
+  </si>
+  <si>
+    <t>5000023266</t>
+  </si>
+  <si>
+    <t>786700005200</t>
+  </si>
+  <si>
+    <t>立式Q1動力電料14mm非AC220_GB,NR12,一般立式中</t>
+  </si>
+  <si>
+    <t>5000023307</t>
+  </si>
+  <si>
+    <t>786700005500</t>
+  </si>
+  <si>
+    <t>立式Q1動力電料22mm非AC220_CE立式中</t>
+  </si>
+  <si>
+    <t>5000023276</t>
+  </si>
+  <si>
     <t>1100101676</t>
   </si>
   <si>
@@ -475,15 +1183,15 @@
     <t>風扇/熱交換器用_6"(HABOR)</t>
   </si>
   <si>
+    <t>0127</t>
+  </si>
+  <si>
+    <t>5000023233</t>
+  </si>
+  <si>
     <t>5000023232</t>
   </si>
   <si>
-    <t>0127</t>
-  </si>
-  <si>
-    <t>5000023233</t>
-  </si>
-  <si>
     <t>1100099048</t>
   </si>
   <si>
@@ -626,6 +1334,24 @@
   </si>
   <si>
     <t>5000023226</t>
+  </si>
+  <si>
+    <t>1100094445</t>
+  </si>
+  <si>
+    <t>925100017300</t>
+  </si>
+  <si>
+    <t>斗笠式刀庫組件/BT40德睿_16T,PRO-1000</t>
+  </si>
+  <si>
+    <t>1D0015</t>
+  </si>
+  <si>
+    <t>0103</t>
+  </si>
+  <si>
+    <t>5000022028</t>
   </si>
   <si>
     <t>採購單</t>
@@ -778,13 +1504,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="12" customWidth="1"/>
     <col min="2" max="2" bestFit="1" width="4" customWidth="1"/>
     <col min="3" max="3" bestFit="1" width="17" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="38" customWidth="1"/>
+    <col min="4" max="4" bestFit="1" width="42" customWidth="1"/>
     <col min="5" max="5" bestFit="1" width="8" customWidth="1"/>
     <col min="6" max="6" bestFit="1" width="6" customWidth="1"/>
     <col min="7" max="7" bestFit="1" width="6" customWidth="1"/>
@@ -799,46 +1525,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>447</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>448</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>449</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>450</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>451</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>210</v>
+        <v>452</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>211</v>
+        <v>453</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>212</v>
+        <v>454</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>213</v>
+        <v>455</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>214</v>
+        <v>456</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>216</v>
+        <v>458</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>217</v>
+        <v>459</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>218</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -876,7 +1602,7 @@
         <v>46141</v>
       </c>
       <c r="L2" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2" t="s">
         <v>8</v>
@@ -896,86 +1622,86 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K3" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L3" s="3">
+        <v>3</v>
+      </c>
+      <c r="M3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" t="s">
         <v>13</v>
-      </c>
-      <c r="J3" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K3" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L3" s="3">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="J4" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K4" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K4" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -984,37 +1710,37 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="J5" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K5" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" t="s">
         <v>22</v>
-      </c>
-      <c r="J5" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K5" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L5" s="3">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1022,16 +1748,16 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
         <v>2</v>
@@ -1040,10 +1766,10 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J6" s="2">
         <v>46141</v>
@@ -1058,12 +1784,12 @@
         <v>8</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -1072,10 +1798,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
         <v>2</v>
@@ -1084,10 +1810,10 @@
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J7" s="2">
         <v>46141</v>
@@ -1096,13 +1822,13 @@
         <v>46141</v>
       </c>
       <c r="L7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="s">
         <v>8</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1119,192 +1845,192 @@
         <v>32</v>
       </c>
       <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
         <v>33</v>
       </c>
-      <c r="F8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>34</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K8" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" t="s">
         <v>35</v>
-      </c>
-      <c r="J8" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K8" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="J9" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K9" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L9" s="3">
+        <v>2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" t="s">
         <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K9" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K10" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" t="s">
         <v>43</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K10" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" t="s">
         <v>48</v>
       </c>
-      <c r="B11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="J11" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K11" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L11" s="3">
+        <v>2</v>
+      </c>
+      <c r="M11" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" t="s">
         <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K11" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L11" s="3">
-        <v>1</v>
-      </c>
-      <c r="M11" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
         <v>52</v>
       </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
         <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>2</v>
       </c>
       <c r="I12" t="s">
         <v>54</v>
@@ -1336,10 +2062,10 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
         <v>2</v>
@@ -1348,10 +2074,10 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J13" s="2">
         <v>46141</v>
@@ -1366,12 +2092,12 @@
         <v>8</v>
       </c>
       <c r="N13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
@@ -1380,10 +2106,10 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
         <v>2</v>
@@ -1392,10 +2118,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J14" s="2">
         <v>46141</v>
@@ -1410,12 +2136,12 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
@@ -1424,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
         <v>2</v>
@@ -1439,7 +2165,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J15" s="2">
         <v>46141</v>
@@ -1454,12 +2180,12 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
@@ -1468,10 +2194,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s">
         <v>2</v>
@@ -1480,10 +2206,10 @@
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="J16" s="2">
         <v>46141</v>
@@ -1492,18 +2218,18 @@
         <v>46141</v>
       </c>
       <c r="L16" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M16" t="s">
         <v>8</v>
       </c>
       <c r="N16" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
@@ -1512,10 +2238,10 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
         <v>2</v>
@@ -1524,10 +2250,10 @@
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="J17" s="2">
         <v>46141</v>
@@ -1542,12 +2268,12 @@
         <v>8</v>
       </c>
       <c r="N17" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
@@ -1556,10 +2282,10 @@
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
         <v>2</v>
@@ -1571,7 +2297,7 @@
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="J18" s="2">
         <v>46141</v>
@@ -1586,12 +2312,12 @@
         <v>8</v>
       </c>
       <c r="N18" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
@@ -1600,10 +2326,10 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
         <v>2</v>
@@ -1615,7 +2341,7 @@
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="J19" s="2">
         <v>46141</v>
@@ -1630,12 +2356,12 @@
         <v>8</v>
       </c>
       <c r="N19" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
@@ -1644,10 +2370,10 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
         <v>2</v>
@@ -1659,7 +2385,7 @@
         <v>2</v>
       </c>
       <c r="I20" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="J20" s="2">
         <v>46141</v>
@@ -1674,12 +2400,12 @@
         <v>8</v>
       </c>
       <c r="N20" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
@@ -1688,10 +2414,10 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F21" t="s">
         <v>2</v>
@@ -1700,10 +2426,10 @@
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="I21" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J21" s="2">
         <v>46141</v>
@@ -1712,18 +2438,18 @@
         <v>46141</v>
       </c>
       <c r="L21" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" t="s">
         <v>8</v>
       </c>
       <c r="N21" t="s">
-        <v>87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
@@ -1732,10 +2458,10 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
         <v>2</v>
@@ -1747,7 +2473,7 @@
         <v>2</v>
       </c>
       <c r="I22" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="J22" s="2">
         <v>46141</v>
@@ -1762,12 +2488,12 @@
         <v>8</v>
       </c>
       <c r="N22" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
@@ -1776,10 +2502,10 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s">
         <v>2</v>
@@ -1791,7 +2517,7 @@
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J23" s="2">
         <v>46141</v>
@@ -1806,12 +2532,12 @@
         <v>8</v>
       </c>
       <c r="N23" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
@@ -1820,10 +2546,10 @@
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F24" t="s">
         <v>2</v>
@@ -1835,7 +2561,7 @@
         <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="J24" s="2">
         <v>46141</v>
@@ -1850,12 +2576,12 @@
         <v>8</v>
       </c>
       <c r="N24" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
@@ -1864,10 +2590,10 @@
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s">
         <v>2</v>
@@ -1879,7 +2605,7 @@
         <v>2</v>
       </c>
       <c r="I25" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="J25" s="2">
         <v>46141</v>
@@ -1894,12 +2620,12 @@
         <v>8</v>
       </c>
       <c r="N25" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
@@ -1908,10 +2634,10 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F26" t="s">
         <v>2</v>
@@ -1923,7 +2649,7 @@
         <v>2</v>
       </c>
       <c r="I26" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="J26" s="2">
         <v>46141</v>
@@ -1932,30 +2658,30 @@
         <v>46141</v>
       </c>
       <c r="L26" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="M26" t="s">
         <v>8</v>
       </c>
       <c r="N26" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s">
         <v>2</v>
@@ -1964,10 +2690,10 @@
         <v>5</v>
       </c>
       <c r="H27" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="I27" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="J27" s="2">
         <v>46141</v>
@@ -1976,18 +2702,18 @@
         <v>46141</v>
       </c>
       <c r="L27" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M27" t="s">
         <v>8</v>
       </c>
       <c r="N27" t="s">
-        <v>101</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
@@ -1996,10 +2722,10 @@
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s">
         <v>2</v>
@@ -2008,10 +2734,10 @@
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="I28" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="J28" s="2">
         <v>46141</v>
@@ -2026,12 +2752,12 @@
         <v>8</v>
       </c>
       <c r="N28" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
@@ -2040,10 +2766,10 @@
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="F29" t="s">
         <v>2</v>
@@ -2052,10 +2778,10 @@
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="I29" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="J29" s="2">
         <v>46141</v>
@@ -2070,12 +2796,12 @@
         <v>8</v>
       </c>
       <c r="N29" t="s">
-        <v>101</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
@@ -2084,10 +2810,10 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
@@ -2099,7 +2825,7 @@
         <v>2</v>
       </c>
       <c r="I30" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="J30" s="2">
         <v>46141</v>
@@ -2114,12 +2840,12 @@
         <v>8</v>
       </c>
       <c r="N30" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
@@ -2128,10 +2854,10 @@
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F31" t="s">
         <v>2</v>
@@ -2143,7 +2869,7 @@
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="J31" s="2">
         <v>46141</v>
@@ -2158,12 +2884,12 @@
         <v>8</v>
       </c>
       <c r="N31" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
@@ -2172,10 +2898,10 @@
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
         <v>2</v>
@@ -2187,7 +2913,7 @@
         <v>2</v>
       </c>
       <c r="I32" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="J32" s="2">
         <v>46141</v>
@@ -2202,12 +2928,12 @@
         <v>8</v>
       </c>
       <c r="N32" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
@@ -2216,10 +2942,10 @@
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s">
         <v>2</v>
@@ -2231,7 +2957,7 @@
         <v>2</v>
       </c>
       <c r="I33" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="J33" s="2">
         <v>46141</v>
@@ -2246,36 +2972,36 @@
         <v>8</v>
       </c>
       <c r="N33" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E34" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="F34" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="G34" t="s">
         <v>5</v>
       </c>
       <c r="H34" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="J34" s="2">
         <v>46141</v>
@@ -2290,36 +3016,36 @@
         <v>8</v>
       </c>
       <c r="N34" t="s">
-        <v>2</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="E35" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="F35" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="G35" t="s">
         <v>5</v>
       </c>
       <c r="H35" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="J35" s="2">
         <v>46141</v>
@@ -2328,7 +3054,7 @@
         <v>46141</v>
       </c>
       <c r="L35" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M35" t="s">
         <v>8</v>
@@ -2339,22 +3065,22 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="E36" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F36" t="s">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="G36" t="s">
         <v>5</v>
@@ -2363,7 +3089,7 @@
         <v>2</v>
       </c>
       <c r="I36" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="J36" s="2">
         <v>46141</v>
@@ -2372,33 +3098,33 @@
         <v>46141</v>
       </c>
       <c r="L36" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" t="s">
         <v>8</v>
       </c>
       <c r="N36" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E37" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="G37" t="s">
         <v>5</v>
@@ -2407,7 +3133,7 @@
         <v>2</v>
       </c>
       <c r="I37" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="J37" s="2">
         <v>46141</v>
@@ -2416,33 +3142,33 @@
         <v>46141</v>
       </c>
       <c r="L37" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" t="s">
         <v>8</v>
       </c>
       <c r="N37" t="s">
-        <v>2</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="E38" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F38" t="s">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="G38" t="s">
         <v>5</v>
@@ -2451,7 +3177,7 @@
         <v>2</v>
       </c>
       <c r="I38" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="J38" s="2">
         <v>46141</v>
@@ -2460,42 +3186,42 @@
         <v>46141</v>
       </c>
       <c r="L38" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" t="s">
         <v>8</v>
       </c>
       <c r="N38" t="s">
-        <v>2</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="E39" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="G39" t="s">
         <v>5</v>
       </c>
       <c r="H39" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="I39" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="J39" s="2">
         <v>46141</v>
@@ -2510,36 +3236,36 @@
         <v>8</v>
       </c>
       <c r="N39" t="s">
-        <v>2</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="E40" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="F40" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="G40" t="s">
         <v>5</v>
       </c>
       <c r="H40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I40" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J40" s="2">
         <v>46141</v>
@@ -2548,7 +3274,7 @@
         <v>46141</v>
       </c>
       <c r="L40" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M40" t="s">
         <v>8</v>
@@ -2559,31 +3285,31 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E41" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="F41" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="G41" t="s">
         <v>5</v>
       </c>
       <c r="H41" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="I41" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="J41" s="2">
         <v>46141</v>
@@ -2598,36 +3324,36 @@
         <v>8</v>
       </c>
       <c r="N41" t="s">
-        <v>2</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E42" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="F42" t="s">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="G42" t="s">
         <v>5</v>
       </c>
       <c r="H42" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="I42" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="J42" s="2">
         <v>46141</v>
@@ -2636,33 +3362,33 @@
         <v>46141</v>
       </c>
       <c r="L42" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M42" t="s">
         <v>8</v>
       </c>
       <c r="N42" t="s">
-        <v>2</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="E43" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="F43" t="s">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="G43" t="s">
         <v>5</v>
@@ -2671,7 +3397,7 @@
         <v>2</v>
       </c>
       <c r="I43" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="J43" s="2">
         <v>46141</v>
@@ -2686,27 +3412,27 @@
         <v>8</v>
       </c>
       <c r="N43" t="s">
-        <v>2</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E44" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="G44" t="s">
         <v>5</v>
@@ -2715,7 +3441,7 @@
         <v>2</v>
       </c>
       <c r="I44" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="J44" s="2">
         <v>46141</v>
@@ -2724,42 +3450,42 @@
         <v>46141</v>
       </c>
       <c r="L44" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M44" t="s">
         <v>8</v>
       </c>
       <c r="N44" t="s">
-        <v>2</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>2</v>
+        <v>189</v>
       </c>
       <c r="B45" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="E45" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="F45" t="s">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="G45" t="s">
         <v>5</v>
       </c>
       <c r="H45" t="s">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="I45" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="J45" s="2">
         <v>46141</v>
@@ -2768,86 +3494,86 @@
         <v>46141</v>
       </c>
       <c r="L45" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="M45" t="s">
         <v>8</v>
       </c>
       <c r="N45" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>176</v>
+        <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="E46" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="F46" t="s">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="G46" t="s">
         <v>5</v>
       </c>
       <c r="H46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" t="s">
+        <v>193</v>
+      </c>
+      <c r="J46" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K46" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L46" s="3">
+        <v>1</v>
+      </c>
+      <c r="M46" t="s">
+        <v>8</v>
+      </c>
+      <c r="N46" t="s">
         <v>179</v>
-      </c>
-      <c r="I46" t="s">
-        <v>180</v>
-      </c>
-      <c r="J46" s="2">
-        <v>46141</v>
-      </c>
-      <c r="K46" s="2">
-        <v>46141</v>
-      </c>
-      <c r="L46" s="3">
-        <v>1</v>
-      </c>
-      <c r="M46" t="s">
-        <v>8</v>
-      </c>
-      <c r="N46" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>2</v>
+        <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E47" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="G47" t="s">
         <v>5</v>
       </c>
       <c r="H47" t="s">
-        <v>184</v>
+        <v>2</v>
       </c>
       <c r="I47" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="J47" s="2">
         <v>46141</v>
@@ -2862,36 +3588,36 @@
         <v>8</v>
       </c>
       <c r="N47" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>2</v>
+        <v>197</v>
       </c>
       <c r="B48" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E48" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="G48" t="s">
         <v>5</v>
       </c>
       <c r="H48" t="s">
-        <v>188</v>
+        <v>2</v>
       </c>
       <c r="I48" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="J48" s="2">
         <v>46141</v>
@@ -2906,36 +3632,36 @@
         <v>8</v>
       </c>
       <c r="N48" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>2</v>
+        <v>199</v>
       </c>
       <c r="B49" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E49" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="F49" t="s">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="G49" t="s">
         <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="I49" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="J49" s="2">
         <v>46141</v>
@@ -2950,36 +3676,36 @@
         <v>8</v>
       </c>
       <c r="N49" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="B50" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
+        <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E50" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="G50" t="s">
         <v>5</v>
       </c>
       <c r="H50" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="I50" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J50" s="2">
         <v>46141</v>
@@ -2994,36 +3720,36 @@
         <v>8</v>
       </c>
       <c r="N50" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>2</v>
+        <v>204</v>
       </c>
       <c r="B51" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>201</v>
+        <v>2</v>
       </c>
       <c r="D51" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E51" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="F51" t="s">
-        <v>203</v>
+        <v>2</v>
       </c>
       <c r="G51" t="s">
         <v>5</v>
       </c>
       <c r="H51" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J51" s="2">
         <v>46141</v>
@@ -3038,46 +3764,3654 @@
         <v>8</v>
       </c>
       <c r="N51" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="6">
-        <v>126</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N52" s="4" t="s">
+      <c r="A52" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>208</v>
+      </c>
+      <c r="D52" t="s">
+        <v>209</v>
+      </c>
+      <c r="E52" t="s">
+        <v>210</v>
+      </c>
+      <c r="F52" t="s">
+        <v>211</v>
+      </c>
+      <c r="G52" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" t="s">
+        <v>212</v>
+      </c>
+      <c r="I52" t="s">
+        <v>213</v>
+      </c>
+      <c r="J52" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K52" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1</v>
+      </c>
+      <c r="M52" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>214</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" t="s">
+        <v>210</v>
+      </c>
+      <c r="F53" t="s">
+        <v>211</v>
+      </c>
+      <c r="G53" t="s">
+        <v>5</v>
+      </c>
+      <c r="H53" t="s">
+        <v>212</v>
+      </c>
+      <c r="I53" t="s">
+        <v>217</v>
+      </c>
+      <c r="J53" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K53" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L53" s="3">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>8</v>
+      </c>
+      <c r="N53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>218</v>
+      </c>
+      <c r="D54" t="s">
+        <v>219</v>
+      </c>
+      <c r="E54" t="s">
+        <v>210</v>
+      </c>
+      <c r="F54" t="s">
+        <v>211</v>
+      </c>
+      <c r="G54" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" t="s">
+        <v>212</v>
+      </c>
+      <c r="I54" t="s">
+        <v>220</v>
+      </c>
+      <c r="J54" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K54" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L54" s="3">
+        <v>5</v>
+      </c>
+      <c r="M54" t="s">
+        <v>8</v>
+      </c>
+      <c r="N54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>221</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>222</v>
+      </c>
+      <c r="D55" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" t="s">
+        <v>224</v>
+      </c>
+      <c r="F55" t="s">
+        <v>225</v>
+      </c>
+      <c r="G55" t="s">
+        <v>5</v>
+      </c>
+      <c r="H55" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" t="s">
+        <v>226</v>
+      </c>
+      <c r="J55" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K55" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L55" s="3">
+        <v>2</v>
+      </c>
+      <c r="M55" t="s">
+        <v>8</v>
+      </c>
+      <c r="N55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>227</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>228</v>
+      </c>
+      <c r="D56" t="s">
+        <v>229</v>
+      </c>
+      <c r="E56" t="s">
+        <v>224</v>
+      </c>
+      <c r="F56" t="s">
+        <v>225</v>
+      </c>
+      <c r="G56" t="s">
+        <v>5</v>
+      </c>
+      <c r="H56" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" t="s">
+        <v>230</v>
+      </c>
+      <c r="J56" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K56" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L56" s="3">
+        <v>2</v>
+      </c>
+      <c r="M56" t="s">
+        <v>8</v>
+      </c>
+      <c r="N56" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>228</v>
+      </c>
+      <c r="D57" t="s">
+        <v>229</v>
+      </c>
+      <c r="E57" t="s">
+        <v>224</v>
+      </c>
+      <c r="F57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G57" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" t="s">
+        <v>2</v>
+      </c>
+      <c r="I57" t="s">
+        <v>231</v>
+      </c>
+      <c r="J57" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K57" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2</v>
+      </c>
+      <c r="M57" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>232</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>233</v>
+      </c>
+      <c r="D58" t="s">
+        <v>234</v>
+      </c>
+      <c r="E58" t="s">
+        <v>235</v>
+      </c>
+      <c r="F58" t="s">
+        <v>211</v>
+      </c>
+      <c r="G58" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" t="s">
+        <v>212</v>
+      </c>
+      <c r="I58" t="s">
+        <v>236</v>
+      </c>
+      <c r="J58" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K58" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L58" s="3">
+        <v>1</v>
+      </c>
+      <c r="M58" t="s">
+        <v>8</v>
+      </c>
+      <c r="N58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>237</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>233</v>
+      </c>
+      <c r="D59" t="s">
+        <v>234</v>
+      </c>
+      <c r="E59" t="s">
+        <v>235</v>
+      </c>
+      <c r="F59" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" t="s">
+        <v>212</v>
+      </c>
+      <c r="I59" t="s">
+        <v>238</v>
+      </c>
+      <c r="J59" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K59" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1</v>
+      </c>
+      <c r="M59" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>239</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>240</v>
+      </c>
+      <c r="D60" t="s">
+        <v>241</v>
+      </c>
+      <c r="E60" t="s">
+        <v>242</v>
+      </c>
+      <c r="F60" t="s">
+        <v>243</v>
+      </c>
+      <c r="G60" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" t="s">
+        <v>162</v>
+      </c>
+      <c r="I60" t="s">
+        <v>244</v>
+      </c>
+      <c r="J60" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K60" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1</v>
+      </c>
+      <c r="M60" t="s">
+        <v>8</v>
+      </c>
+      <c r="N60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>245</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>246</v>
+      </c>
+      <c r="D61" t="s">
+        <v>247</v>
+      </c>
+      <c r="E61" t="s">
+        <v>242</v>
+      </c>
+      <c r="F61" t="s">
+        <v>243</v>
+      </c>
+      <c r="G61" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" t="s">
+        <v>112</v>
+      </c>
+      <c r="I61" t="s">
+        <v>248</v>
+      </c>
+      <c r="J61" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K61" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1</v>
+      </c>
+      <c r="M61" t="s">
+        <v>8</v>
+      </c>
+      <c r="N61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>249</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>250</v>
+      </c>
+      <c r="D62" t="s">
+        <v>251</v>
+      </c>
+      <c r="E62" t="s">
+        <v>252</v>
+      </c>
+      <c r="F62" t="s">
+        <v>243</v>
+      </c>
+      <c r="G62" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" t="s">
+        <v>253</v>
+      </c>
+      <c r="I62" t="s">
+        <v>254</v>
+      </c>
+      <c r="J62" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K62" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L62" s="3">
+        <v>1</v>
+      </c>
+      <c r="M62" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>255</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>256</v>
+      </c>
+      <c r="D63" t="s">
+        <v>257</v>
+      </c>
+      <c r="E63" t="s">
+        <v>252</v>
+      </c>
+      <c r="F63" t="s">
+        <v>243</v>
+      </c>
+      <c r="G63" t="s">
+        <v>5</v>
+      </c>
+      <c r="H63" t="s">
+        <v>258</v>
+      </c>
+      <c r="I63" t="s">
+        <v>259</v>
+      </c>
+      <c r="J63" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K63" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L63" s="3">
+        <v>1</v>
+      </c>
+      <c r="M63" t="s">
+        <v>8</v>
+      </c>
+      <c r="N63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" t="s">
+        <v>260</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>261</v>
+      </c>
+      <c r="D64" t="s">
+        <v>262</v>
+      </c>
+      <c r="E64" t="s">
+        <v>252</v>
+      </c>
+      <c r="F64" t="s">
+        <v>243</v>
+      </c>
+      <c r="G64" t="s">
+        <v>5</v>
+      </c>
+      <c r="H64" t="s">
+        <v>263</v>
+      </c>
+      <c r="I64" t="s">
+        <v>264</v>
+      </c>
+      <c r="J64" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K64" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L64" s="3">
+        <v>1</v>
+      </c>
+      <c r="M64" t="s">
+        <v>8</v>
+      </c>
+      <c r="N64" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" t="s">
+        <v>265</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>266</v>
+      </c>
+      <c r="D65" t="s">
+        <v>267</v>
+      </c>
+      <c r="E65" t="s">
+        <v>252</v>
+      </c>
+      <c r="F65" t="s">
+        <v>243</v>
+      </c>
+      <c r="G65" t="s">
+        <v>5</v>
+      </c>
+      <c r="H65" t="s">
+        <v>268</v>
+      </c>
+      <c r="I65" t="s">
+        <v>269</v>
+      </c>
+      <c r="J65" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K65" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L65" s="3">
+        <v>1</v>
+      </c>
+      <c r="M65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>271</v>
+      </c>
+      <c r="D66" t="s">
+        <v>272</v>
+      </c>
+      <c r="E66" t="s">
+        <v>252</v>
+      </c>
+      <c r="F66" t="s">
+        <v>243</v>
+      </c>
+      <c r="G66" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" t="s">
+        <v>273</v>
+      </c>
+      <c r="I66" t="s">
+        <v>274</v>
+      </c>
+      <c r="J66" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K66" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L66" s="3">
+        <v>1</v>
+      </c>
+      <c r="M66" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" t="s">
+        <v>275</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>276</v>
+      </c>
+      <c r="D67" t="s">
+        <v>277</v>
+      </c>
+      <c r="E67" t="s">
+        <v>252</v>
+      </c>
+      <c r="F67" t="s">
+        <v>243</v>
+      </c>
+      <c r="G67" t="s">
+        <v>5</v>
+      </c>
+      <c r="H67" t="s">
+        <v>278</v>
+      </c>
+      <c r="I67" t="s">
+        <v>279</v>
+      </c>
+      <c r="J67" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K67" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L67" s="3">
+        <v>1</v>
+      </c>
+      <c r="M67" t="s">
+        <v>8</v>
+      </c>
+      <c r="N67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" t="s">
+        <v>280</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>281</v>
+      </c>
+      <c r="D68" t="s">
+        <v>282</v>
+      </c>
+      <c r="E68" t="s">
+        <v>242</v>
+      </c>
+      <c r="F68" t="s">
+        <v>243</v>
+      </c>
+      <c r="G68" t="s">
+        <v>5</v>
+      </c>
+      <c r="H68" t="s">
+        <v>283</v>
+      </c>
+      <c r="I68" t="s">
+        <v>284</v>
+      </c>
+      <c r="J68" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K68" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L68" s="3">
+        <v>1</v>
+      </c>
+      <c r="M68" t="s">
+        <v>8</v>
+      </c>
+      <c r="N68" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" t="s">
+        <v>285</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>286</v>
+      </c>
+      <c r="D69" t="s">
+        <v>287</v>
+      </c>
+      <c r="E69" t="s">
+        <v>242</v>
+      </c>
+      <c r="F69" t="s">
+        <v>243</v>
+      </c>
+      <c r="G69" t="s">
+        <v>5</v>
+      </c>
+      <c r="H69" t="s">
+        <v>288</v>
+      </c>
+      <c r="I69" t="s">
+        <v>289</v>
+      </c>
+      <c r="J69" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K69" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L69" s="3">
+        <v>1</v>
+      </c>
+      <c r="M69" t="s">
+        <v>8</v>
+      </c>
+      <c r="N69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" t="s">
+        <v>290</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>291</v>
+      </c>
+      <c r="D70" t="s">
+        <v>292</v>
+      </c>
+      <c r="E70" t="s">
+        <v>252</v>
+      </c>
+      <c r="F70" t="s">
+        <v>243</v>
+      </c>
+      <c r="G70" t="s">
+        <v>5</v>
+      </c>
+      <c r="H70" t="s">
+        <v>293</v>
+      </c>
+      <c r="I70" t="s">
+        <v>294</v>
+      </c>
+      <c r="J70" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K70" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L70" s="3">
+        <v>1</v>
+      </c>
+      <c r="M70" t="s">
+        <v>8</v>
+      </c>
+      <c r="N70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" t="s">
+        <v>280</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" t="s">
+        <v>295</v>
+      </c>
+      <c r="D71" t="s">
+        <v>296</v>
+      </c>
+      <c r="E71" t="s">
+        <v>242</v>
+      </c>
+      <c r="F71" t="s">
+        <v>243</v>
+      </c>
+      <c r="G71" t="s">
+        <v>5</v>
+      </c>
+      <c r="H71" t="s">
+        <v>283</v>
+      </c>
+      <c r="I71" t="s">
+        <v>297</v>
+      </c>
+      <c r="J71" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K71" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L71" s="3">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
+        <v>8</v>
+      </c>
+      <c r="N71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" t="s">
+        <v>249</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>295</v>
+      </c>
+      <c r="D72" t="s">
+        <v>296</v>
+      </c>
+      <c r="E72" t="s">
+        <v>252</v>
+      </c>
+      <c r="F72" t="s">
+        <v>243</v>
+      </c>
+      <c r="G72" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" t="s">
+        <v>253</v>
+      </c>
+      <c r="I72" t="s">
+        <v>298</v>
+      </c>
+      <c r="J72" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K72" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L72" s="3">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" t="s">
+        <v>285</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>295</v>
+      </c>
+      <c r="D73" t="s">
+        <v>296</v>
+      </c>
+      <c r="E73" t="s">
+        <v>242</v>
+      </c>
+      <c r="F73" t="s">
+        <v>243</v>
+      </c>
+      <c r="G73" t="s">
+        <v>5</v>
+      </c>
+      <c r="H73" t="s">
+        <v>288</v>
+      </c>
+      <c r="I73" t="s">
+        <v>299</v>
+      </c>
+      <c r="J73" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K73" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L73" s="3">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
+        <v>8</v>
+      </c>
+      <c r="N73" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" t="s">
+        <v>255</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
+        <v>295</v>
+      </c>
+      <c r="D74" t="s">
+        <v>296</v>
+      </c>
+      <c r="E74" t="s">
+        <v>252</v>
+      </c>
+      <c r="F74" t="s">
+        <v>243</v>
+      </c>
+      <c r="G74" t="s">
+        <v>5</v>
+      </c>
+      <c r="H74" t="s">
+        <v>258</v>
+      </c>
+      <c r="I74" t="s">
+        <v>300</v>
+      </c>
+      <c r="J74" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K74" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L74" s="3">
+        <v>1</v>
+      </c>
+      <c r="M74" t="s">
+        <v>8</v>
+      </c>
+      <c r="N74" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" t="s">
+        <v>290</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>295</v>
+      </c>
+      <c r="D75" t="s">
+        <v>296</v>
+      </c>
+      <c r="E75" t="s">
+        <v>252</v>
+      </c>
+      <c r="F75" t="s">
+        <v>243</v>
+      </c>
+      <c r="G75" t="s">
+        <v>5</v>
+      </c>
+      <c r="H75" t="s">
+        <v>293</v>
+      </c>
+      <c r="I75" t="s">
+        <v>301</v>
+      </c>
+      <c r="J75" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K75" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L75" s="3">
+        <v>1</v>
+      </c>
+      <c r="M75" t="s">
+        <v>8</v>
+      </c>
+      <c r="N75" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76" t="s">
+        <v>270</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>295</v>
+      </c>
+      <c r="D76" t="s">
+        <v>296</v>
+      </c>
+      <c r="E76" t="s">
+        <v>252</v>
+      </c>
+      <c r="F76" t="s">
+        <v>243</v>
+      </c>
+      <c r="G76" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" t="s">
+        <v>273</v>
+      </c>
+      <c r="I76" t="s">
+        <v>302</v>
+      </c>
+      <c r="J76" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K76" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L76" s="3">
+        <v>1</v>
+      </c>
+      <c r="M76" t="s">
+        <v>8</v>
+      </c>
+      <c r="N76" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" t="s">
+        <v>245</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>295</v>
+      </c>
+      <c r="D77" t="s">
+        <v>296</v>
+      </c>
+      <c r="E77" t="s">
+        <v>242</v>
+      </c>
+      <c r="F77" t="s">
+        <v>243</v>
+      </c>
+      <c r="G77" t="s">
+        <v>5</v>
+      </c>
+      <c r="H77" t="s">
+        <v>112</v>
+      </c>
+      <c r="I77" t="s">
+        <v>303</v>
+      </c>
+      <c r="J77" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K77" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L77" s="3">
+        <v>1</v>
+      </c>
+      <c r="M77" t="s">
+        <v>8</v>
+      </c>
+      <c r="N77" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
+      <c r="A78" t="s">
+        <v>290</v>
+      </c>
+      <c r="B78" t="s">
+        <v>304</v>
+      </c>
+      <c r="C78" t="s">
+        <v>305</v>
+      </c>
+      <c r="D78" t="s">
+        <v>306</v>
+      </c>
+      <c r="E78" t="s">
+        <v>252</v>
+      </c>
+      <c r="F78" t="s">
+        <v>243</v>
+      </c>
+      <c r="G78" t="s">
+        <v>5</v>
+      </c>
+      <c r="H78" t="s">
+        <v>293</v>
+      </c>
+      <c r="I78" t="s">
+        <v>307</v>
+      </c>
+      <c r="J78" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K78" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L78" s="3">
+        <v>1</v>
+      </c>
+      <c r="M78" t="s">
+        <v>8</v>
+      </c>
+      <c r="N78" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" t="s">
+        <v>285</v>
+      </c>
+      <c r="B79" t="s">
+        <v>304</v>
+      </c>
+      <c r="C79" t="s">
+        <v>308</v>
+      </c>
+      <c r="D79" t="s">
+        <v>309</v>
+      </c>
+      <c r="E79" t="s">
+        <v>242</v>
+      </c>
+      <c r="F79" t="s">
+        <v>243</v>
+      </c>
+      <c r="G79" t="s">
+        <v>5</v>
+      </c>
+      <c r="H79" t="s">
+        <v>288</v>
+      </c>
+      <c r="I79" t="s">
+        <v>310</v>
+      </c>
+      <c r="J79" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K79" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L79" s="3">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>8</v>
+      </c>
+      <c r="N79" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
+      <c r="A80" t="s">
+        <v>280</v>
+      </c>
+      <c r="B80" t="s">
+        <v>304</v>
+      </c>
+      <c r="C80" t="s">
+        <v>308</v>
+      </c>
+      <c r="D80" t="s">
+        <v>309</v>
+      </c>
+      <c r="E80" t="s">
+        <v>242</v>
+      </c>
+      <c r="F80" t="s">
+        <v>243</v>
+      </c>
+      <c r="G80" t="s">
+        <v>5</v>
+      </c>
+      <c r="H80" t="s">
+        <v>283</v>
+      </c>
+      <c r="I80" t="s">
+        <v>311</v>
+      </c>
+      <c r="J80" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K80" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L80" s="3">
+        <v>1</v>
+      </c>
+      <c r="M80" t="s">
+        <v>8</v>
+      </c>
+      <c r="N80" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" t="s">
+        <v>290</v>
+      </c>
+      <c r="B81" t="s">
+        <v>312</v>
+      </c>
+      <c r="C81" t="s">
+        <v>308</v>
+      </c>
+      <c r="D81" t="s">
+        <v>309</v>
+      </c>
+      <c r="E81" t="s">
+        <v>252</v>
+      </c>
+      <c r="F81" t="s">
+        <v>243</v>
+      </c>
+      <c r="G81" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" t="s">
+        <v>293</v>
+      </c>
+      <c r="I81" t="s">
+        <v>313</v>
+      </c>
+      <c r="J81" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K81" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L81" s="3">
+        <v>1</v>
+      </c>
+      <c r="M81" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" t="s">
+        <v>245</v>
+      </c>
+      <c r="B82" t="s">
+        <v>304</v>
+      </c>
+      <c r="C82" t="s">
+        <v>308</v>
+      </c>
+      <c r="D82" t="s">
+        <v>309</v>
+      </c>
+      <c r="E82" t="s">
+        <v>242</v>
+      </c>
+      <c r="F82" t="s">
+        <v>243</v>
+      </c>
+      <c r="G82" t="s">
+        <v>5</v>
+      </c>
+      <c r="H82" t="s">
+        <v>112</v>
+      </c>
+      <c r="I82" t="s">
+        <v>314</v>
+      </c>
+      <c r="J82" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K82" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L82" s="3">
+        <v>1</v>
+      </c>
+      <c r="M82" t="s">
+        <v>8</v>
+      </c>
+      <c r="N82" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" t="s">
+        <v>270</v>
+      </c>
+      <c r="B83" t="s">
+        <v>304</v>
+      </c>
+      <c r="C83" t="s">
+        <v>308</v>
+      </c>
+      <c r="D83" t="s">
+        <v>309</v>
+      </c>
+      <c r="E83" t="s">
+        <v>252</v>
+      </c>
+      <c r="F83" t="s">
+        <v>243</v>
+      </c>
+      <c r="G83" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" t="s">
+        <v>273</v>
+      </c>
+      <c r="I83" t="s">
+        <v>315</v>
+      </c>
+      <c r="J83" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K83" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L83" s="3">
+        <v>1</v>
+      </c>
+      <c r="M83" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" t="s">
+        <v>265</v>
+      </c>
+      <c r="B84" t="s">
+        <v>243</v>
+      </c>
+      <c r="C84" t="s">
+        <v>308</v>
+      </c>
+      <c r="D84" t="s">
+        <v>309</v>
+      </c>
+      <c r="E84" t="s">
+        <v>252</v>
+      </c>
+      <c r="F84" t="s">
+        <v>243</v>
+      </c>
+      <c r="G84" t="s">
+        <v>5</v>
+      </c>
+      <c r="H84" t="s">
+        <v>268</v>
+      </c>
+      <c r="I84" t="s">
+        <v>316</v>
+      </c>
+      <c r="J84" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K84" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L84" s="3">
+        <v>2</v>
+      </c>
+      <c r="M84" t="s">
+        <v>8</v>
+      </c>
+      <c r="N84" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" t="s">
+        <v>270</v>
+      </c>
+      <c r="B85" t="s">
+        <v>312</v>
+      </c>
+      <c r="C85" t="s">
+        <v>317</v>
+      </c>
+      <c r="D85" t="s">
+        <v>318</v>
+      </c>
+      <c r="E85" t="s">
+        <v>252</v>
+      </c>
+      <c r="F85" t="s">
+        <v>243</v>
+      </c>
+      <c r="G85" t="s">
+        <v>5</v>
+      </c>
+      <c r="H85" t="s">
+        <v>273</v>
+      </c>
+      <c r="I85" t="s">
+        <v>319</v>
+      </c>
+      <c r="J85" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K85" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L85" s="3">
+        <v>1</v>
+      </c>
+      <c r="M85" t="s">
+        <v>8</v>
+      </c>
+      <c r="N85" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" t="s">
+        <v>275</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
+        <v>317</v>
+      </c>
+      <c r="D86" t="s">
+        <v>318</v>
+      </c>
+      <c r="E86" t="s">
+        <v>252</v>
+      </c>
+      <c r="F86" t="s">
+        <v>243</v>
+      </c>
+      <c r="G86" t="s">
+        <v>5</v>
+      </c>
+      <c r="H86" t="s">
+        <v>278</v>
+      </c>
+      <c r="I86" t="s">
+        <v>320</v>
+      </c>
+      <c r="J86" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K86" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L86" s="3">
+        <v>1</v>
+      </c>
+      <c r="M86" t="s">
+        <v>8</v>
+      </c>
+      <c r="N86" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" t="s">
+        <v>285</v>
+      </c>
+      <c r="B87" t="s">
+        <v>312</v>
+      </c>
+      <c r="C87" t="s">
+        <v>317</v>
+      </c>
+      <c r="D87" t="s">
+        <v>318</v>
+      </c>
+      <c r="E87" t="s">
+        <v>242</v>
+      </c>
+      <c r="F87" t="s">
+        <v>243</v>
+      </c>
+      <c r="G87" t="s">
+        <v>5</v>
+      </c>
+      <c r="H87" t="s">
+        <v>288</v>
+      </c>
+      <c r="I87" t="s">
+        <v>321</v>
+      </c>
+      <c r="J87" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K87" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L87" s="3">
+        <v>1</v>
+      </c>
+      <c r="M87" t="s">
+        <v>8</v>
+      </c>
+      <c r="N87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="A88" t="s">
+        <v>290</v>
+      </c>
+      <c r="B88" t="s">
+        <v>243</v>
+      </c>
+      <c r="C88" t="s">
+        <v>317</v>
+      </c>
+      <c r="D88" t="s">
+        <v>318</v>
+      </c>
+      <c r="E88" t="s">
+        <v>252</v>
+      </c>
+      <c r="F88" t="s">
+        <v>243</v>
+      </c>
+      <c r="G88" t="s">
+        <v>5</v>
+      </c>
+      <c r="H88" t="s">
+        <v>293</v>
+      </c>
+      <c r="I88" t="s">
+        <v>322</v>
+      </c>
+      <c r="J88" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K88" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L88" s="3">
+        <v>1</v>
+      </c>
+      <c r="M88" t="s">
+        <v>8</v>
+      </c>
+      <c r="N88" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89" t="s">
+        <v>265</v>
+      </c>
+      <c r="B89" t="s">
+        <v>312</v>
+      </c>
+      <c r="C89" t="s">
+        <v>317</v>
+      </c>
+      <c r="D89" t="s">
+        <v>318</v>
+      </c>
+      <c r="E89" t="s">
+        <v>252</v>
+      </c>
+      <c r="F89" t="s">
+        <v>243</v>
+      </c>
+      <c r="G89" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" t="s">
+        <v>268</v>
+      </c>
+      <c r="I89" t="s">
+        <v>323</v>
+      </c>
+      <c r="J89" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K89" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L89" s="3">
+        <v>1</v>
+      </c>
+      <c r="M89" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90" t="s">
+        <v>255</v>
+      </c>
+      <c r="B90" t="s">
+        <v>304</v>
+      </c>
+      <c r="C90" t="s">
+        <v>317</v>
+      </c>
+      <c r="D90" t="s">
+        <v>318</v>
+      </c>
+      <c r="E90" t="s">
+        <v>252</v>
+      </c>
+      <c r="F90" t="s">
+        <v>243</v>
+      </c>
+      <c r="G90" t="s">
+        <v>5</v>
+      </c>
+      <c r="H90" t="s">
+        <v>258</v>
+      </c>
+      <c r="I90" t="s">
+        <v>324</v>
+      </c>
+      <c r="J90" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K90" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L90" s="3">
+        <v>1</v>
+      </c>
+      <c r="M90" t="s">
+        <v>8</v>
+      </c>
+      <c r="N90" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" t="s">
+        <v>280</v>
+      </c>
+      <c r="B91" t="s">
+        <v>312</v>
+      </c>
+      <c r="C91" t="s">
+        <v>317</v>
+      </c>
+      <c r="D91" t="s">
+        <v>318</v>
+      </c>
+      <c r="E91" t="s">
+        <v>242</v>
+      </c>
+      <c r="F91" t="s">
+        <v>243</v>
+      </c>
+      <c r="G91" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" t="s">
+        <v>283</v>
+      </c>
+      <c r="I91" t="s">
+        <v>325</v>
+      </c>
+      <c r="J91" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K91" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L91" s="3">
+        <v>2</v>
+      </c>
+      <c r="M91" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92" t="s">
+        <v>249</v>
+      </c>
+      <c r="B92" t="s">
+        <v>304</v>
+      </c>
+      <c r="C92" t="s">
+        <v>317</v>
+      </c>
+      <c r="D92" t="s">
+        <v>318</v>
+      </c>
+      <c r="E92" t="s">
+        <v>252</v>
+      </c>
+      <c r="F92" t="s">
+        <v>243</v>
+      </c>
+      <c r="G92" t="s">
+        <v>5</v>
+      </c>
+      <c r="H92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I92" t="s">
+        <v>326</v>
+      </c>
+      <c r="J92" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K92" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L92" s="3">
+        <v>1</v>
+      </c>
+      <c r="M92" t="s">
+        <v>8</v>
+      </c>
+      <c r="N92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
+      <c r="A93" t="s">
+        <v>265</v>
+      </c>
+      <c r="B93" t="s">
+        <v>304</v>
+      </c>
+      <c r="C93" t="s">
+        <v>327</v>
+      </c>
+      <c r="D93" t="s">
+        <v>328</v>
+      </c>
+      <c r="E93" t="s">
+        <v>252</v>
+      </c>
+      <c r="F93" t="s">
+        <v>243</v>
+      </c>
+      <c r="G93" t="s">
+        <v>5</v>
+      </c>
+      <c r="H93" t="s">
+        <v>268</v>
+      </c>
+      <c r="I93" t="s">
+        <v>329</v>
+      </c>
+      <c r="J93" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K93" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L93" s="3">
+        <v>1</v>
+      </c>
+      <c r="M93" t="s">
+        <v>8</v>
+      </c>
+      <c r="N93" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
+      <c r="A94" t="s">
+        <v>280</v>
+      </c>
+      <c r="B94" t="s">
+        <v>243</v>
+      </c>
+      <c r="C94" t="s">
+        <v>327</v>
+      </c>
+      <c r="D94" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" t="s">
+        <v>242</v>
+      </c>
+      <c r="F94" t="s">
+        <v>243</v>
+      </c>
+      <c r="G94" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" t="s">
+        <v>283</v>
+      </c>
+      <c r="I94" t="s">
+        <v>330</v>
+      </c>
+      <c r="J94" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K94" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L94" s="3">
+        <v>1</v>
+      </c>
+      <c r="M94" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
+      <c r="A95" t="s">
+        <v>265</v>
+      </c>
+      <c r="B95" t="s">
+        <v>331</v>
+      </c>
+      <c r="C95" t="s">
+        <v>332</v>
+      </c>
+      <c r="D95" t="s">
+        <v>333</v>
+      </c>
+      <c r="E95" t="s">
+        <v>252</v>
+      </c>
+      <c r="F95" t="s">
+        <v>243</v>
+      </c>
+      <c r="G95" t="s">
+        <v>5</v>
+      </c>
+      <c r="H95" t="s">
+        <v>268</v>
+      </c>
+      <c r="I95" t="s">
+        <v>334</v>
+      </c>
+      <c r="J95" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K95" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L95" s="3">
+        <v>1</v>
+      </c>
+      <c r="M95" t="s">
+        <v>8</v>
+      </c>
+      <c r="N95" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
+      <c r="A96" t="s">
+        <v>255</v>
+      </c>
+      <c r="B96" t="s">
+        <v>312</v>
+      </c>
+      <c r="C96" t="s">
+        <v>332</v>
+      </c>
+      <c r="D96" t="s">
+        <v>333</v>
+      </c>
+      <c r="E96" t="s">
+        <v>252</v>
+      </c>
+      <c r="F96" t="s">
+        <v>243</v>
+      </c>
+      <c r="G96" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" t="s">
+        <v>258</v>
+      </c>
+      <c r="I96" t="s">
+        <v>335</v>
+      </c>
+      <c r="J96" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K96" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L96" s="3">
+        <v>1</v>
+      </c>
+      <c r="M96" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="A97" t="s">
+        <v>249</v>
+      </c>
+      <c r="B97" t="s">
+        <v>312</v>
+      </c>
+      <c r="C97" t="s">
+        <v>332</v>
+      </c>
+      <c r="D97" t="s">
+        <v>333</v>
+      </c>
+      <c r="E97" t="s">
+        <v>252</v>
+      </c>
+      <c r="F97" t="s">
+        <v>243</v>
+      </c>
+      <c r="G97" t="s">
+        <v>5</v>
+      </c>
+      <c r="H97" t="s">
+        <v>253</v>
+      </c>
+      <c r="I97" t="s">
+        <v>336</v>
+      </c>
+      <c r="J97" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K97" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L97" s="3">
+        <v>1</v>
+      </c>
+      <c r="M97" t="s">
+        <v>8</v>
+      </c>
+      <c r="N97" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
+      <c r="A98" t="s">
+        <v>265</v>
+      </c>
+      <c r="B98" t="s">
+        <v>337</v>
+      </c>
+      <c r="C98" t="s">
+        <v>338</v>
+      </c>
+      <c r="D98" t="s">
+        <v>339</v>
+      </c>
+      <c r="E98" t="s">
+        <v>252</v>
+      </c>
+      <c r="F98" t="s">
+        <v>243</v>
+      </c>
+      <c r="G98" t="s">
+        <v>5</v>
+      </c>
+      <c r="H98" t="s">
+        <v>268</v>
+      </c>
+      <c r="I98" t="s">
+        <v>340</v>
+      </c>
+      <c r="J98" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K98" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L98" s="3">
+        <v>1</v>
+      </c>
+      <c r="M98" t="s">
+        <v>8</v>
+      </c>
+      <c r="N98" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
+      <c r="A99" t="s">
+        <v>290</v>
+      </c>
+      <c r="B99" t="s">
+        <v>331</v>
+      </c>
+      <c r="C99" t="s">
+        <v>338</v>
+      </c>
+      <c r="D99" t="s">
+        <v>339</v>
+      </c>
+      <c r="E99" t="s">
+        <v>252</v>
+      </c>
+      <c r="F99" t="s">
+        <v>243</v>
+      </c>
+      <c r="G99" t="s">
+        <v>5</v>
+      </c>
+      <c r="H99" t="s">
+        <v>293</v>
+      </c>
+      <c r="I99" t="s">
+        <v>341</v>
+      </c>
+      <c r="J99" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K99" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L99" s="3">
+        <v>1</v>
+      </c>
+      <c r="M99" t="s">
+        <v>8</v>
+      </c>
+      <c r="N99" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="A100" t="s">
+        <v>280</v>
+      </c>
+      <c r="B100" t="s">
+        <v>331</v>
+      </c>
+      <c r="C100" t="s">
+        <v>338</v>
+      </c>
+      <c r="D100" t="s">
+        <v>339</v>
+      </c>
+      <c r="E100" t="s">
+        <v>242</v>
+      </c>
+      <c r="F100" t="s">
+        <v>243</v>
+      </c>
+      <c r="G100" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" t="s">
+        <v>283</v>
+      </c>
+      <c r="I100" t="s">
+        <v>342</v>
+      </c>
+      <c r="J100" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K100" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L100" s="3">
+        <v>1</v>
+      </c>
+      <c r="M100" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
+      <c r="A101" t="s">
+        <v>239</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>343</v>
+      </c>
+      <c r="D101" t="s">
+        <v>344</v>
+      </c>
+      <c r="E101" t="s">
+        <v>242</v>
+      </c>
+      <c r="F101" t="s">
+        <v>243</v>
+      </c>
+      <c r="G101" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" t="s">
+        <v>162</v>
+      </c>
+      <c r="I101" t="s">
+        <v>345</v>
+      </c>
+      <c r="J101" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K101" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L101" s="3">
+        <v>1</v>
+      </c>
+      <c r="M101" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" t="s">
+        <v>260</v>
+      </c>
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" t="s">
+        <v>343</v>
+      </c>
+      <c r="D102" t="s">
+        <v>344</v>
+      </c>
+      <c r="E102" t="s">
+        <v>252</v>
+      </c>
+      <c r="F102" t="s">
+        <v>243</v>
+      </c>
+      <c r="G102" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" t="s">
+        <v>263</v>
+      </c>
+      <c r="I102" t="s">
+        <v>346</v>
+      </c>
+      <c r="J102" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K102" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L102" s="3">
+        <v>1</v>
+      </c>
+      <c r="M102" t="s">
+        <v>8</v>
+      </c>
+      <c r="N102" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="A103" t="s">
+        <v>260</v>
+      </c>
+      <c r="B103" t="s">
+        <v>304</v>
+      </c>
+      <c r="C103" t="s">
+        <v>347</v>
+      </c>
+      <c r="D103" t="s">
+        <v>348</v>
+      </c>
+      <c r="E103" t="s">
+        <v>252</v>
+      </c>
+      <c r="F103" t="s">
+        <v>243</v>
+      </c>
+      <c r="G103" t="s">
+        <v>5</v>
+      </c>
+      <c r="H103" t="s">
+        <v>263</v>
+      </c>
+      <c r="I103" t="s">
+        <v>349</v>
+      </c>
+      <c r="J103" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K103" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L103" s="3">
+        <v>1</v>
+      </c>
+      <c r="M103" t="s">
+        <v>8</v>
+      </c>
+      <c r="N103" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
+      <c r="A104" t="s">
+        <v>239</v>
+      </c>
+      <c r="B104" t="s">
+        <v>304</v>
+      </c>
+      <c r="C104" t="s">
+        <v>350</v>
+      </c>
+      <c r="D104" t="s">
+        <v>351</v>
+      </c>
+      <c r="E104" t="s">
+        <v>242</v>
+      </c>
+      <c r="F104" t="s">
+        <v>243</v>
+      </c>
+      <c r="G104" t="s">
+        <v>5</v>
+      </c>
+      <c r="H104" t="s">
+        <v>162</v>
+      </c>
+      <c r="I104" t="s">
+        <v>352</v>
+      </c>
+      <c r="J104" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K104" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L104" s="3">
+        <v>1</v>
+      </c>
+      <c r="M104" t="s">
+        <v>8</v>
+      </c>
+      <c r="N104" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
+      <c r="A105" t="s">
+        <v>260</v>
+      </c>
+      <c r="B105" t="s">
+        <v>312</v>
+      </c>
+      <c r="C105" t="s">
+        <v>350</v>
+      </c>
+      <c r="D105" t="s">
+        <v>351</v>
+      </c>
+      <c r="E105" t="s">
+        <v>252</v>
+      </c>
+      <c r="F105" t="s">
+        <v>243</v>
+      </c>
+      <c r="G105" t="s">
+        <v>5</v>
+      </c>
+      <c r="H105" t="s">
+        <v>263</v>
+      </c>
+      <c r="I105" t="s">
+        <v>353</v>
+      </c>
+      <c r="J105" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K105" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L105" s="3">
+        <v>1</v>
+      </c>
+      <c r="M105" t="s">
+        <v>8</v>
+      </c>
+      <c r="N105" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
+      <c r="A106" t="s">
+        <v>260</v>
+      </c>
+      <c r="B106" t="s">
+        <v>243</v>
+      </c>
+      <c r="C106" t="s">
+        <v>354</v>
+      </c>
+      <c r="D106" t="s">
+        <v>355</v>
+      </c>
+      <c r="E106" t="s">
+        <v>252</v>
+      </c>
+      <c r="F106" t="s">
+        <v>243</v>
+      </c>
+      <c r="G106" t="s">
+        <v>5</v>
+      </c>
+      <c r="H106" t="s">
+        <v>263</v>
+      </c>
+      <c r="I106" t="s">
+        <v>356</v>
+      </c>
+      <c r="J106" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K106" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L106" s="3">
+        <v>1</v>
+      </c>
+      <c r="M106" t="s">
+        <v>8</v>
+      </c>
+      <c r="N106" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
+      <c r="A107" t="s">
+        <v>265</v>
+      </c>
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>357</v>
+      </c>
+      <c r="D107" t="s">
+        <v>358</v>
+      </c>
+      <c r="E107" t="s">
+        <v>252</v>
+      </c>
+      <c r="F107" t="s">
+        <v>243</v>
+      </c>
+      <c r="G107" t="s">
+        <v>5</v>
+      </c>
+      <c r="H107" t="s">
+        <v>268</v>
+      </c>
+      <c r="I107" t="s">
+        <v>359</v>
+      </c>
+      <c r="J107" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K107" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L107" s="3">
+        <v>1</v>
+      </c>
+      <c r="M107" t="s">
+        <v>8</v>
+      </c>
+      <c r="N107" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
+      <c r="A108" t="s">
+        <v>249</v>
+      </c>
+      <c r="B108" t="s">
+        <v>243</v>
+      </c>
+      <c r="C108" t="s">
+        <v>360</v>
+      </c>
+      <c r="D108" t="s">
+        <v>361</v>
+      </c>
+      <c r="E108" t="s">
+        <v>252</v>
+      </c>
+      <c r="F108" t="s">
+        <v>243</v>
+      </c>
+      <c r="G108" t="s">
+        <v>5</v>
+      </c>
+      <c r="H108" t="s">
+        <v>253</v>
+      </c>
+      <c r="I108" t="s">
+        <v>362</v>
+      </c>
+      <c r="J108" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K108" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L108" s="3">
+        <v>1</v>
+      </c>
+      <c r="M108" t="s">
+        <v>8</v>
+      </c>
+      <c r="N108" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
+      <c r="A109" t="s">
+        <v>260</v>
+      </c>
+      <c r="B109" t="s">
+        <v>331</v>
+      </c>
+      <c r="C109" t="s">
+        <v>360</v>
+      </c>
+      <c r="D109" t="s">
+        <v>361</v>
+      </c>
+      <c r="E109" t="s">
+        <v>252</v>
+      </c>
+      <c r="F109" t="s">
+        <v>243</v>
+      </c>
+      <c r="G109" t="s">
+        <v>5</v>
+      </c>
+      <c r="H109" t="s">
+        <v>263</v>
+      </c>
+      <c r="I109" t="s">
+        <v>363</v>
+      </c>
+      <c r="J109" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K109" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L109" s="3">
+        <v>1</v>
+      </c>
+      <c r="M109" t="s">
+        <v>8</v>
+      </c>
+      <c r="N109" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
+      <c r="A110" t="s">
+        <v>255</v>
+      </c>
+      <c r="B110" t="s">
+        <v>243</v>
+      </c>
+      <c r="C110" t="s">
+        <v>360</v>
+      </c>
+      <c r="D110" t="s">
+        <v>361</v>
+      </c>
+      <c r="E110" t="s">
+        <v>252</v>
+      </c>
+      <c r="F110" t="s">
+        <v>243</v>
+      </c>
+      <c r="G110" t="s">
+        <v>5</v>
+      </c>
+      <c r="H110" t="s">
+        <v>258</v>
+      </c>
+      <c r="I110" t="s">
+        <v>364</v>
+      </c>
+      <c r="J110" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K110" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L110" s="3">
+        <v>1</v>
+      </c>
+      <c r="M110" t="s">
+        <v>8</v>
+      </c>
+      <c r="N110" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
+      <c r="A111" t="s">
+        <v>280</v>
+      </c>
+      <c r="B111" t="s">
+        <v>337</v>
+      </c>
+      <c r="C111" t="s">
+        <v>360</v>
+      </c>
+      <c r="D111" t="s">
+        <v>361</v>
+      </c>
+      <c r="E111" t="s">
+        <v>242</v>
+      </c>
+      <c r="F111" t="s">
+        <v>243</v>
+      </c>
+      <c r="G111" t="s">
+        <v>5</v>
+      </c>
+      <c r="H111" t="s">
+        <v>283</v>
+      </c>
+      <c r="I111" t="s">
+        <v>365</v>
+      </c>
+      <c r="J111" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K111" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L111" s="3">
+        <v>1</v>
+      </c>
+      <c r="M111" t="s">
+        <v>8</v>
+      </c>
+      <c r="N111" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
+      <c r="A112" t="s">
+        <v>239</v>
+      </c>
+      <c r="B112" t="s">
+        <v>312</v>
+      </c>
+      <c r="C112" t="s">
+        <v>366</v>
+      </c>
+      <c r="D112" t="s">
+        <v>367</v>
+      </c>
+      <c r="E112" t="s">
+        <v>242</v>
+      </c>
+      <c r="F112" t="s">
+        <v>243</v>
+      </c>
+      <c r="G112" t="s">
+        <v>5</v>
+      </c>
+      <c r="H112" t="s">
+        <v>162</v>
+      </c>
+      <c r="I112" t="s">
+        <v>368</v>
+      </c>
+      <c r="J112" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K112" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L112" s="3">
+        <v>1</v>
+      </c>
+      <c r="M112" t="s">
+        <v>8</v>
+      </c>
+      <c r="N112" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
+      <c r="A113" t="s">
+        <v>285</v>
+      </c>
+      <c r="B113" t="s">
+        <v>243</v>
+      </c>
+      <c r="C113" t="s">
+        <v>366</v>
+      </c>
+      <c r="D113" t="s">
+        <v>367</v>
+      </c>
+      <c r="E113" t="s">
+        <v>242</v>
+      </c>
+      <c r="F113" t="s">
+        <v>243</v>
+      </c>
+      <c r="G113" t="s">
+        <v>5</v>
+      </c>
+      <c r="H113" t="s">
+        <v>288</v>
+      </c>
+      <c r="I113" t="s">
+        <v>369</v>
+      </c>
+      <c r="J113" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K113" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L113" s="3">
+        <v>1</v>
+      </c>
+      <c r="M113" t="s">
+        <v>8</v>
+      </c>
+      <c r="N113" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14">
+      <c r="A114" t="s">
+        <v>275</v>
+      </c>
+      <c r="B114" t="s">
+        <v>304</v>
+      </c>
+      <c r="C114" t="s">
+        <v>366</v>
+      </c>
+      <c r="D114" t="s">
+        <v>367</v>
+      </c>
+      <c r="E114" t="s">
+        <v>252</v>
+      </c>
+      <c r="F114" t="s">
+        <v>243</v>
+      </c>
+      <c r="G114" t="s">
+        <v>5</v>
+      </c>
+      <c r="H114" t="s">
+        <v>278</v>
+      </c>
+      <c r="I114" t="s">
+        <v>370</v>
+      </c>
+      <c r="J114" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K114" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L114" s="3">
+        <v>1</v>
+      </c>
+      <c r="M114" t="s">
+        <v>8</v>
+      </c>
+      <c r="N114" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
+      <c r="A115" t="s">
+        <v>249</v>
+      </c>
+      <c r="B115" t="s">
+        <v>331</v>
+      </c>
+      <c r="C115" t="s">
+        <v>371</v>
+      </c>
+      <c r="D115" t="s">
+        <v>372</v>
+      </c>
+      <c r="E115" t="s">
+        <v>252</v>
+      </c>
+      <c r="F115" t="s">
+        <v>243</v>
+      </c>
+      <c r="G115" t="s">
+        <v>5</v>
+      </c>
+      <c r="H115" t="s">
+        <v>253</v>
+      </c>
+      <c r="I115" t="s">
+        <v>373</v>
+      </c>
+      <c r="J115" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K115" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L115" s="3">
+        <v>1</v>
+      </c>
+      <c r="M115" t="s">
+        <v>8</v>
+      </c>
+      <c r="N115" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
+      <c r="A116" t="s">
+        <v>260</v>
+      </c>
+      <c r="B116" t="s">
+        <v>337</v>
+      </c>
+      <c r="C116" t="s">
+        <v>371</v>
+      </c>
+      <c r="D116" t="s">
+        <v>372</v>
+      </c>
+      <c r="E116" t="s">
+        <v>252</v>
+      </c>
+      <c r="F116" t="s">
+        <v>243</v>
+      </c>
+      <c r="G116" t="s">
+        <v>5</v>
+      </c>
+      <c r="H116" t="s">
+        <v>263</v>
+      </c>
+      <c r="I116" t="s">
+        <v>374</v>
+      </c>
+      <c r="J116" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K116" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L116" s="3">
+        <v>1</v>
+      </c>
+      <c r="M116" t="s">
+        <v>8</v>
+      </c>
+      <c r="N116" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
+      <c r="A117" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" t="s">
+        <v>331</v>
+      </c>
+      <c r="C117" t="s">
+        <v>371</v>
+      </c>
+      <c r="D117" t="s">
+        <v>372</v>
+      </c>
+      <c r="E117" t="s">
+        <v>252</v>
+      </c>
+      <c r="F117" t="s">
+        <v>243</v>
+      </c>
+      <c r="G117" t="s">
+        <v>5</v>
+      </c>
+      <c r="H117" t="s">
+        <v>258</v>
+      </c>
+      <c r="I117" t="s">
+        <v>375</v>
+      </c>
+      <c r="J117" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K117" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L117" s="3">
+        <v>1</v>
+      </c>
+      <c r="M117" t="s">
+        <v>8</v>
+      </c>
+      <c r="N117" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
+      <c r="A118" t="s">
+        <v>280</v>
+      </c>
+      <c r="B118" t="s">
+        <v>376</v>
+      </c>
+      <c r="C118" t="s">
+        <v>371</v>
+      </c>
+      <c r="D118" t="s">
+        <v>372</v>
+      </c>
+      <c r="E118" t="s">
+        <v>242</v>
+      </c>
+      <c r="F118" t="s">
+        <v>243</v>
+      </c>
+      <c r="G118" t="s">
+        <v>5</v>
+      </c>
+      <c r="H118" t="s">
+        <v>283</v>
+      </c>
+      <c r="I118" t="s">
+        <v>377</v>
+      </c>
+      <c r="J118" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K118" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L118" s="3">
+        <v>1</v>
+      </c>
+      <c r="M118" t="s">
+        <v>8</v>
+      </c>
+      <c r="N118" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
+      <c r="A119" t="s">
+        <v>270</v>
+      </c>
+      <c r="B119" t="s">
+        <v>243</v>
+      </c>
+      <c r="C119" t="s">
+        <v>378</v>
+      </c>
+      <c r="D119" t="s">
+        <v>379</v>
+      </c>
+      <c r="E119" t="s">
+        <v>252</v>
+      </c>
+      <c r="F119" t="s">
+        <v>243</v>
+      </c>
+      <c r="G119" t="s">
+        <v>5</v>
+      </c>
+      <c r="H119" t="s">
+        <v>273</v>
+      </c>
+      <c r="I119" t="s">
+        <v>380</v>
+      </c>
+      <c r="J119" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K119" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L119" s="3">
+        <v>1</v>
+      </c>
+      <c r="M119" t="s">
+        <v>8</v>
+      </c>
+      <c r="N119" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14">
+      <c r="A120" t="s">
+        <v>245</v>
+      </c>
+      <c r="B120" t="s">
+        <v>312</v>
+      </c>
+      <c r="C120" t="s">
+        <v>381</v>
+      </c>
+      <c r="D120" t="s">
+        <v>382</v>
+      </c>
+      <c r="E120" t="s">
+        <v>242</v>
+      </c>
+      <c r="F120" t="s">
+        <v>243</v>
+      </c>
+      <c r="G120" t="s">
+        <v>5</v>
+      </c>
+      <c r="H120" t="s">
+        <v>112</v>
+      </c>
+      <c r="I120" t="s">
+        <v>383</v>
+      </c>
+      <c r="J120" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K120" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L120" s="3">
+        <v>1</v>
+      </c>
+      <c r="M120" t="s">
+        <v>8</v>
+      </c>
+      <c r="N120" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
+      <c r="A121" t="s">
+        <v>290</v>
+      </c>
+      <c r="B121" t="s">
+        <v>337</v>
+      </c>
+      <c r="C121" t="s">
+        <v>384</v>
+      </c>
+      <c r="D121" t="s">
+        <v>385</v>
+      </c>
+      <c r="E121" t="s">
+        <v>252</v>
+      </c>
+      <c r="F121" t="s">
+        <v>243</v>
+      </c>
+      <c r="G121" t="s">
+        <v>5</v>
+      </c>
+      <c r="H121" t="s">
+        <v>293</v>
+      </c>
+      <c r="I121" t="s">
+        <v>386</v>
+      </c>
+      <c r="J121" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K121" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L121" s="3">
+        <v>1</v>
+      </c>
+      <c r="M121" t="s">
+        <v>8</v>
+      </c>
+      <c r="N121" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
+      <c r="A122" t="s">
+        <v>387</v>
+      </c>
+      <c r="B122" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" t="s">
+        <v>388</v>
+      </c>
+      <c r="D122" t="s">
+        <v>389</v>
+      </c>
+      <c r="E122" t="s">
+        <v>210</v>
+      </c>
+      <c r="F122" t="s">
+        <v>390</v>
+      </c>
+      <c r="G122" t="s">
+        <v>5</v>
+      </c>
+      <c r="H122" t="s">
+        <v>212</v>
+      </c>
+      <c r="I122" t="s">
+        <v>391</v>
+      </c>
+      <c r="J122" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K122" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L122" s="3">
+        <v>8</v>
+      </c>
+      <c r="M122" t="s">
+        <v>8</v>
+      </c>
+      <c r="N122" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14">
+      <c r="A123" t="s">
+        <v>387</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" t="s">
+        <v>388</v>
+      </c>
+      <c r="D123" t="s">
+        <v>389</v>
+      </c>
+      <c r="E123" t="s">
+        <v>210</v>
+      </c>
+      <c r="F123" t="s">
+        <v>211</v>
+      </c>
+      <c r="G123" t="s">
+        <v>5</v>
+      </c>
+      <c r="H123" t="s">
+        <v>212</v>
+      </c>
+      <c r="I123" t="s">
+        <v>392</v>
+      </c>
+      <c r="J123" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K123" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L123" s="3">
+        <v>1</v>
+      </c>
+      <c r="M123" t="s">
+        <v>8</v>
+      </c>
+      <c r="N123" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
+      <c r="A124" t="s">
+        <v>393</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s">
+        <v>394</v>
+      </c>
+      <c r="D124" t="s">
+        <v>395</v>
+      </c>
+      <c r="E124" t="s">
+        <v>396</v>
+      </c>
+      <c r="F124" t="s">
+        <v>397</v>
+      </c>
+      <c r="G124" t="s">
+        <v>5</v>
+      </c>
+      <c r="H124" t="s">
+        <v>2</v>
+      </c>
+      <c r="I124" t="s">
+        <v>398</v>
+      </c>
+      <c r="J124" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K124" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L124" s="3">
+        <v>1</v>
+      </c>
+      <c r="M124" t="s">
+        <v>8</v>
+      </c>
+      <c r="N124" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
+      <c r="A125" t="s">
+        <v>399</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1</v>
+      </c>
+      <c r="C125" t="s">
+        <v>400</v>
+      </c>
+      <c r="D125" t="s">
+        <v>401</v>
+      </c>
+      <c r="E125" t="s">
+        <v>402</v>
+      </c>
+      <c r="F125" t="s">
+        <v>403</v>
+      </c>
+      <c r="G125" t="s">
+        <v>5</v>
+      </c>
+      <c r="H125" t="s">
+        <v>2</v>
+      </c>
+      <c r="I125" t="s">
+        <v>404</v>
+      </c>
+      <c r="J125" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K125" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L125" s="3">
+        <v>3</v>
+      </c>
+      <c r="M125" t="s">
+        <v>8</v>
+      </c>
+      <c r="N125" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14">
+      <c r="A126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>405</v>
+      </c>
+      <c r="C126" t="s">
+        <v>406</v>
+      </c>
+      <c r="D126" t="s">
+        <v>407</v>
+      </c>
+      <c r="E126" t="s">
+        <v>2</v>
+      </c>
+      <c r="F126" t="s">
+        <v>408</v>
+      </c>
+      <c r="G126" t="s">
+        <v>5</v>
+      </c>
+      <c r="H126" t="s">
+        <v>409</v>
+      </c>
+      <c r="I126" t="s">
+        <v>410</v>
+      </c>
+      <c r="J126" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K126" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L126" s="3">
+        <v>40</v>
+      </c>
+      <c r="M126" t="s">
+        <v>8</v>
+      </c>
+      <c r="N126" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
+      <c r="A127" t="s">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>405</v>
+      </c>
+      <c r="C127" t="s">
+        <v>412</v>
+      </c>
+      <c r="D127" t="s">
+        <v>413</v>
+      </c>
+      <c r="E127" t="s">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>414</v>
+      </c>
+      <c r="G127" t="s">
+        <v>5</v>
+      </c>
+      <c r="H127" t="s">
+        <v>415</v>
+      </c>
+      <c r="I127" t="s">
+        <v>416</v>
+      </c>
+      <c r="J127" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K127" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L127" s="3">
+        <v>1</v>
+      </c>
+      <c r="M127" t="s">
+        <v>8</v>
+      </c>
+      <c r="N127" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
+      <c r="A128" t="s">
+        <v>2</v>
+      </c>
+      <c r="B128" t="s">
+        <v>405</v>
+      </c>
+      <c r="C128" t="s">
+        <v>418</v>
+      </c>
+      <c r="D128" t="s">
+        <v>419</v>
+      </c>
+      <c r="E128" t="s">
+        <v>2</v>
+      </c>
+      <c r="F128" t="s">
+        <v>414</v>
+      </c>
+      <c r="G128" t="s">
+        <v>5</v>
+      </c>
+      <c r="H128" t="s">
+        <v>420</v>
+      </c>
+      <c r="I128" t="s">
+        <v>421</v>
+      </c>
+      <c r="J128" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K128" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L128" s="3">
+        <v>1</v>
+      </c>
+      <c r="M128" t="s">
+        <v>8</v>
+      </c>
+      <c r="N128" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" t="s">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s">
+        <v>405</v>
+      </c>
+      <c r="C129" t="s">
+        <v>422</v>
+      </c>
+      <c r="D129" t="s">
+        <v>423</v>
+      </c>
+      <c r="E129" t="s">
+        <v>2</v>
+      </c>
+      <c r="F129" t="s">
+        <v>414</v>
+      </c>
+      <c r="G129" t="s">
+        <v>5</v>
+      </c>
+      <c r="H129" t="s">
+        <v>424</v>
+      </c>
+      <c r="I129" t="s">
+        <v>425</v>
+      </c>
+      <c r="J129" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K129" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L129" s="3">
+        <v>1</v>
+      </c>
+      <c r="M129" t="s">
+        <v>8</v>
+      </c>
+      <c r="N129" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14">
+      <c r="A130" t="s">
+        <v>2</v>
+      </c>
+      <c r="B130" t="s">
+        <v>405</v>
+      </c>
+      <c r="C130" t="s">
+        <v>427</v>
+      </c>
+      <c r="D130" t="s">
+        <v>428</v>
+      </c>
+      <c r="E130" t="s">
+        <v>2</v>
+      </c>
+      <c r="F130" t="s">
+        <v>414</v>
+      </c>
+      <c r="G130" t="s">
+        <v>5</v>
+      </c>
+      <c r="H130" t="s">
+        <v>429</v>
+      </c>
+      <c r="I130" t="s">
+        <v>430</v>
+      </c>
+      <c r="J130" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K130" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L130" s="3">
+        <v>1</v>
+      </c>
+      <c r="M130" t="s">
+        <v>8</v>
+      </c>
+      <c r="N130" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
+      <c r="A131" t="s">
+        <v>2</v>
+      </c>
+      <c r="B131" t="s">
+        <v>405</v>
+      </c>
+      <c r="C131" t="s">
+        <v>432</v>
+      </c>
+      <c r="D131" t="s">
+        <v>433</v>
+      </c>
+      <c r="E131" t="s">
+        <v>2</v>
+      </c>
+      <c r="F131" t="s">
+        <v>403</v>
+      </c>
+      <c r="G131" t="s">
+        <v>5</v>
+      </c>
+      <c r="H131" t="s">
+        <v>434</v>
+      </c>
+      <c r="I131" t="s">
+        <v>435</v>
+      </c>
+      <c r="J131" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K131" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L131" s="3">
+        <v>1</v>
+      </c>
+      <c r="M131" t="s">
+        <v>8</v>
+      </c>
+      <c r="N131" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14">
+      <c r="A132" t="s">
+        <v>2</v>
+      </c>
+      <c r="B132" t="s">
+        <v>405</v>
+      </c>
+      <c r="C132" t="s">
+        <v>437</v>
+      </c>
+      <c r="D132" t="s">
+        <v>438</v>
+      </c>
+      <c r="E132" t="s">
+        <v>2</v>
+      </c>
+      <c r="F132" t="s">
+        <v>439</v>
+      </c>
+      <c r="G132" t="s">
+        <v>5</v>
+      </c>
+      <c r="H132" t="s">
+        <v>65</v>
+      </c>
+      <c r="I132" t="s">
+        <v>440</v>
+      </c>
+      <c r="J132" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K132" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L132" s="3">
+        <v>1</v>
+      </c>
+      <c r="M132" t="s">
+        <v>8</v>
+      </c>
+      <c r="N132" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14">
+      <c r="A133" t="s">
+        <v>441</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1</v>
+      </c>
+      <c r="C133" t="s">
+        <v>442</v>
+      </c>
+      <c r="D133" t="s">
+        <v>443</v>
+      </c>
+      <c r="E133" t="s">
+        <v>444</v>
+      </c>
+      <c r="F133" t="s">
+        <v>445</v>
+      </c>
+      <c r="G133" t="s">
+        <v>5</v>
+      </c>
+      <c r="H133" t="s">
+        <v>2</v>
+      </c>
+      <c r="I133" t="s">
+        <v>446</v>
+      </c>
+      <c r="J133" s="2">
+        <v>46141</v>
+      </c>
+      <c r="K133" s="2">
+        <v>46141</v>
+      </c>
+      <c r="L133" s="3">
+        <v>1</v>
+      </c>
+      <c r="M133" t="s">
+        <v>8</v>
+      </c>
+      <c r="N133" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14">
+      <c r="A134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J134" s="5"/>
+      <c r="K134" s="5"/>
+      <c r="L134" s="6">
+        <v>223</v>
+      </c>
+      <c r="M134" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N134" s="4" t="s">
         <v>2</v>
       </c>
     </row>
